--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124663398</v>
+        <v>124664322</v>
       </c>
       <c r="B3" t="n">
-        <v>91632</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R3" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664322</v>
+        <v>124663398</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>91632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720870</v>
+        <v>720795</v>
       </c>
       <c r="R4" t="n">
-        <v>6626379</v>
+        <v>6626271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124664292</v>
+        <v>124664322</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124664322</v>
+        <v>124663398</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>91632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720870</v>
+        <v>720795</v>
       </c>
       <c r="R3" t="n">
-        <v>6626379</v>
+        <v>6626271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124663398</v>
+        <v>124664292</v>
       </c>
       <c r="B4" t="n">
-        <v>91632</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R4" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124664322</v>
+        <v>124663398</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>91632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720870</v>
+        <v>720795</v>
       </c>
       <c r="R2" t="n">
-        <v>6626379</v>
+        <v>6626271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124663398</v>
+        <v>124664322</v>
       </c>
       <c r="B3" t="n">
-        <v>91632</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R3" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664292</v>
+        <v>124665953</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>98123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720870</v>
+        <v>720564</v>
       </c>
       <c r="R4" t="n">
-        <v>6626379</v>
+        <v>6626375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124665953</v>
+        <v>124664292</v>
       </c>
       <c r="B5" t="n">
-        <v>98123</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720564</v>
+        <v>720870</v>
       </c>
       <c r="R5" t="n">
-        <v>6626375</v>
+        <v>6626379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124663398</v>
+        <v>124664322</v>
       </c>
       <c r="B2" t="n">
-        <v>91632</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R2" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124664322</v>
+        <v>124664292</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124665953</v>
+        <v>124663398</v>
       </c>
       <c r="B4" t="n">
-        <v>98123</v>
+        <v>91632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,43 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720564</v>
+        <v>720795</v>
       </c>
       <c r="R4" t="n">
-        <v>6626375</v>
+        <v>6626271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664292</v>
+        <v>124665953</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>98123</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720870</v>
+        <v>720564</v>
       </c>
       <c r="R5" t="n">
-        <v>6626379</v>
+        <v>6626375</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124664322</v>
+        <v>124664292</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124664292</v>
+        <v>124665953</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>98123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720870</v>
+        <v>720564</v>
       </c>
       <c r="R3" t="n">
-        <v>6626379</v>
+        <v>6626375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124663398</v>
+        <v>124664322</v>
       </c>
       <c r="B4" t="n">
-        <v>91632</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R4" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124665953</v>
+        <v>124663398</v>
       </c>
       <c r="B5" t="n">
-        <v>98123</v>
+        <v>91632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,43 +1006,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720564</v>
+        <v>720795</v>
       </c>
       <c r="R5" t="n">
-        <v>6626375</v>
+        <v>6626271</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124664292</v>
+        <v>124664322</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664322</v>
+        <v>124663398</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>91632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,34 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720870</v>
+        <v>720795</v>
       </c>
       <c r="R4" t="n">
-        <v>6626379</v>
+        <v>6626271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124663398</v>
+        <v>124664292</v>
       </c>
       <c r="B5" t="n">
-        <v>91632</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R5" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124665953</v>
+        <v>124663398</v>
       </c>
       <c r="B3" t="n">
-        <v>98123</v>
+        <v>91632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720564</v>
+        <v>720795</v>
       </c>
       <c r="R3" t="n">
-        <v>6626375</v>
+        <v>6626271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124663398</v>
+        <v>124664292</v>
       </c>
       <c r="B4" t="n">
-        <v>91632</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R4" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664292</v>
+        <v>124665953</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>98123</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720870</v>
+        <v>720564</v>
       </c>
       <c r="R5" t="n">
-        <v>6626379</v>
+        <v>6626375</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124664322</v>
+        <v>124664292</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664292</v>
+        <v>124665953</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>98123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720870</v>
+        <v>720564</v>
       </c>
       <c r="R4" t="n">
-        <v>6626379</v>
+        <v>6626375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124665953</v>
+        <v>124664322</v>
       </c>
       <c r="B5" t="n">
-        <v>98123</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,43 +1006,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720564</v>
+        <v>720870</v>
       </c>
       <c r="R5" t="n">
-        <v>6626375</v>
+        <v>6626379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124664292</v>
+        <v>124663398</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720870</v>
+        <v>720795</v>
       </c>
       <c r="R2" t="n">
-        <v>6626379</v>
+        <v>6626271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124663398</v>
+        <v>124665953</v>
       </c>
       <c r="B3" t="n">
-        <v>91632</v>
+        <v>98123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720795</v>
+        <v>720564</v>
       </c>
       <c r="R3" t="n">
-        <v>6626271</v>
+        <v>6626375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124665953</v>
+        <v>124664322</v>
       </c>
       <c r="B4" t="n">
-        <v>98123</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,43 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720564</v>
+        <v>720870</v>
       </c>
       <c r="R4" t="n">
-        <v>6626375</v>
+        <v>6626379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664322</v>
+        <v>124664292</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124663398</v>
+        <v>124664322</v>
       </c>
       <c r="B2" t="n">
-        <v>91632</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R2" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664322</v>
+        <v>124664292</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664292</v>
+        <v>124663398</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720870</v>
+        <v>720795</v>
       </c>
       <c r="R5" t="n">
-        <v>6626379</v>
+        <v>6626271</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124664322</v>
+        <v>124663398</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>91632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720870</v>
+        <v>720795</v>
       </c>
       <c r="R2" t="n">
-        <v>6626379</v>
+        <v>6626271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664292</v>
+        <v>124664322</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124663398</v>
+        <v>124664292</v>
       </c>
       <c r="B5" t="n">
-        <v>91632</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720795</v>
+        <v>720870</v>
       </c>
       <c r="R5" t="n">
-        <v>6626271</v>
+        <v>6626379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124663398</v>
       </c>
       <c r="B2" t="n">
-        <v>91632</v>
+        <v>91792</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>124665953</v>
       </c>
       <c r="B3" t="n">
-        <v>98123</v>
+        <v>98291</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664322</v>
+        <v>124664292</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664292</v>
+        <v>124664322</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>100451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124665953</v>
+        <v>124664292</v>
       </c>
       <c r="B3" t="n">
-        <v>98291</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720564</v>
+        <v>720870</v>
       </c>
       <c r="R3" t="n">
-        <v>6626375</v>
+        <v>6626379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664292</v>
+        <v>124665953</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
+        <v>98291</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720870</v>
+        <v>720564</v>
       </c>
       <c r="R4" t="n">
-        <v>6626379</v>
+        <v>6626375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>91792</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>LC</t>
@@ -777,50 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124664292</v>
+        <v>124665953</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720870</v>
+        <v>720564</v>
       </c>
       <c r="R3" t="n">
-        <v>6626379</v>
+        <v>6626375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124665953</v>
+        <v>124664322</v>
       </c>
       <c r="B4" t="n">
-        <v>98291</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Holmängsviken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720564</v>
+        <v>720870</v>
       </c>
       <c r="R4" t="n">
-        <v>6626375</v>
+        <v>6626379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,37 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664322</v>
+        <v>124664292</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,6 +1070,4292 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128985878</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626378</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128985894</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720563</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626412</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128985884</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98658</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720568</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626387</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128985897</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720543</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626360</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128985905</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720491</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6626322</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128985886</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720581</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6626397</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128985900</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720544</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6626397</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128985854</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720559</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6626267</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128985888</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720578</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6626426</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128985863</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720755</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6626301</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128985903</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92787</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>150</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720482</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6626323</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128985887</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105686</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720586</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6626407</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128985866</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92137</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720790</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6626254</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128985861</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720733</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6626258</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128985860</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91720</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720709</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6626266</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128985890</v>
+      </c>
+      <c r="B21" t="n">
+        <v>86864</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720530</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6626415</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128985850</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720528</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6626273</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128985839</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720497</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6626297</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128985904</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92810</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720496</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6626331</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128985862</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91017</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720770</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6626291</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128985901</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720521</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6626398</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128985891</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79504</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720531</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6626414</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128985853</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92787</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>150</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720573</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6626278</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128985898</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91281</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720530</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6626369</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128985907</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100824</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720516</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6626359</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128985883</v>
+      </c>
+      <c r="B31" t="n">
+        <v>89415</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>37</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jättekamskivling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Amanita ceciliae</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; Broome) Bas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720621</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6626429</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128985865</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720780</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6626277</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128985893</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58579</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720574</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6626394</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128985908</v>
+      </c>
+      <c r="B34" t="n">
+        <v>86939</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720504</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6626377</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128985852</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720548</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6626285</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128985889</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720564</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6626459</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128985876</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720766</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6626378</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128985879</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720754</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6626384</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128985859</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720718</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6626247</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128985906</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92787</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>150</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720486</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6626330</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128985885</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720573</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6626380</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128985895</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720572</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6626395</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128985882</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91877</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720643</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6626413</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128985873</v>
+      </c>
+      <c r="B44" t="n">
+        <v>86855</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>445</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kopparspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>720771</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6626378</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128985896</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720577</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6626370</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128985902</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720521</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6626387</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128985875</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6626395</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128985899</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58577</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>720542</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6626391</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,45 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R6" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1151,6 +1154,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,48 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92834</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R7" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1251,7 +1252,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>98658</v>
+        <v>92834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R8" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1349,6 +1352,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1367,7 +1371,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B9" t="n">
         <v>92834</v>
@@ -1405,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R9" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>98658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,37 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R10" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1550,7 +1551,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985886</v>
+        <v>128985854</v>
       </c>
       <c r="B11" t="n">
-        <v>92443</v>
+        <v>92834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,34 +1580,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720581</v>
+        <v>720559</v>
       </c>
       <c r="R11" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1648,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985900</v>
+        <v>128985888</v>
       </c>
       <c r="B12" t="n">
-        <v>92443</v>
+        <v>92834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1677,34 +1681,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720544</v>
+        <v>720578</v>
       </c>
       <c r="R12" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1745,6 +1752,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1763,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B13" t="n">
-        <v>92834</v>
+        <v>92443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1774,37 +1782,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R13" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1845,7 +1850,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B14" t="n">
-        <v>92834</v>
+        <v>92443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,37 +1879,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R14" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1946,7 +1947,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,48 +1965,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>92787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2044,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92787</v>
+        <v>92834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B17" t="n">
-        <v>105686</v>
+        <v>92834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,34 +2174,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R17" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,6 +2245,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2357,48 +2361,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985861</v>
+        <v>128985860</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>91720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>1106</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720733</v>
+        <v>720709</v>
       </c>
       <c r="R19" t="n">
-        <v>6626258</v>
+        <v>6626266</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,7 +2440,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2458,32 +2458,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985860</v>
+        <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>91720</v>
+        <v>105686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1106</v>
+        <v>224098</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720709</v>
+        <v>720586</v>
       </c>
       <c r="R20" t="n">
-        <v>6626266</v>
+        <v>6626407</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3547,45 +3547,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B31" t="n">
-        <v>89415</v>
+        <v>92834</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R31" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3620,17 +3623,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3649,10 +3648,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985865</v>
+        <v>128985893</v>
       </c>
       <c r="B32" t="n">
-        <v>92834</v>
+        <v>58579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,37 +3659,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720780</v>
+        <v>720574</v>
       </c>
       <c r="R32" t="n">
-        <v>6626277</v>
+        <v>6626394</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3731,7 +3727,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3750,32 +3745,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985893</v>
+        <v>128985883</v>
       </c>
       <c r="B33" t="n">
-        <v>58579</v>
+        <v>89415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208249</v>
+        <v>37</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720574</v>
+        <v>720621</v>
       </c>
       <c r="R33" t="n">
-        <v>6626394</v>
+        <v>6626429</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3821,6 +3816,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B34" t="n">
-        <v>86939</v>
+        <v>92443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R34" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985852</v>
+        <v>128985859</v>
       </c>
       <c r="B35" t="n">
-        <v>92834</v>
+        <v>92443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,37 +3955,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720548</v>
+        <v>720718</v>
       </c>
       <c r="R35" t="n">
-        <v>6626285</v>
+        <v>6626247</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4026,7 +4023,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4045,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985889</v>
+        <v>128985908</v>
       </c>
       <c r="B36" t="n">
-        <v>92834</v>
+        <v>86939</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4056,37 +4052,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720564</v>
+        <v>720504</v>
       </c>
       <c r="R36" t="n">
-        <v>6626459</v>
+        <v>6626377</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4127,7 +4120,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4138,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985876</v>
+        <v>128985852</v>
       </c>
       <c r="B37" t="n">
-        <v>92443</v>
+        <v>92834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4157,34 +4149,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720766</v>
+        <v>720548</v>
       </c>
       <c r="R37" t="n">
-        <v>6626378</v>
+        <v>6626285</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4225,6 +4220,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4243,7 +4239,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985879</v>
+        <v>128985889</v>
       </c>
       <c r="B38" t="n">
         <v>92834</v>
@@ -4281,10 +4277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720754</v>
+        <v>720564</v>
       </c>
       <c r="R38" t="n">
-        <v>6626384</v>
+        <v>6626459</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4344,10 +4340,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985859</v>
+        <v>128985879</v>
       </c>
       <c r="B39" t="n">
-        <v>92443</v>
+        <v>92834</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4355,34 +4351,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720718</v>
+        <v>720754</v>
       </c>
       <c r="R39" t="n">
-        <v>6626247</v>
+        <v>6626384</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4423,6 +4422,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985882</v>
+        <v>128985896</v>
       </c>
       <c r="B43" t="n">
-        <v>91877</v>
+        <v>92834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720643</v>
+        <v>720577</v>
       </c>
       <c r="R43" t="n">
-        <v>6626413</v>
+        <v>6626370</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4816,39 +4816,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4865,45 +4841,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B44" t="n">
-        <v>86855</v>
+        <v>92834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R44" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4944,6 +4923,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4962,10 +4942,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B45" t="n">
-        <v>92834</v>
+        <v>92443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4973,37 +4953,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R45" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5044,7 +5021,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5063,10 +5039,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985902</v>
+        <v>128985899</v>
       </c>
       <c r="B46" t="n">
-        <v>92443</v>
+        <v>58577</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5074,21 +5050,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>208250</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5098,10 +5074,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720521</v>
+        <v>720542</v>
       </c>
       <c r="R46" t="n">
-        <v>6626387</v>
+        <v>6626391</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5160,48 +5136,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985875</v>
+        <v>128985873</v>
       </c>
       <c r="B47" t="n">
-        <v>92834</v>
+        <v>86855</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720769</v>
+        <v>720771</v>
       </c>
       <c r="R47" t="n">
-        <v>6626395</v>
+        <v>6626378</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5242,7 +5215,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5261,45 +5233,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B48" t="n">
-        <v>58577</v>
+        <v>91877</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R48" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5334,6 +5309,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5342,6 +5322,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,48 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R6" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1154,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,45 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R7" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1252,6 +1251,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>128985905</v>
       </c>
       <c r="B9" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,37 +1580,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R11" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1651,7 +1648,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1666,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,37 +1677,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R12" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1752,7 +1745,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1771,10 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985900</v>
+        <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,34 +1774,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720544</v>
+        <v>720559</v>
       </c>
       <c r="R13" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1850,6 +1845,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1868,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,34 +1875,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R14" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1947,6 +1946,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985861</v>
+        <v>128985866</v>
       </c>
       <c r="B17" t="n">
-        <v>92834</v>
+        <v>92142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,37 +2174,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720733</v>
+        <v>720790</v>
       </c>
       <c r="R17" t="n">
-        <v>6626258</v>
+        <v>6626254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2245,7 +2242,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2264,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B18" t="n">
-        <v>92137</v>
+        <v>91725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2299,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R18" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2361,45 +2357,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985860</v>
+        <v>128985861</v>
       </c>
       <c r="B19" t="n">
-        <v>91720</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1106</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720709</v>
+        <v>720733</v>
       </c>
       <c r="R19" t="n">
-        <v>6626266</v>
+        <v>6626258</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2440,6 +2439,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>105686</v>
+        <v>105693</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B24" t="n">
-        <v>92810</v>
+        <v>91022</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R24" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B25" t="n">
-        <v>91017</v>
+        <v>92815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R25" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>128985891</v>
       </c>
       <c r="B27" t="n">
-        <v>79504</v>
+        <v>79409</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,48 +3547,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985865</v>
+        <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>92834</v>
+        <v>89420</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720780</v>
+        <v>720621</v>
       </c>
       <c r="R31" t="n">
-        <v>6626277</v>
+        <v>6626429</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3623,13 +3620,17 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3648,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985893</v>
+        <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>58579</v>
+        <v>92839</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3659,34 +3660,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208249</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720574</v>
+        <v>720780</v>
       </c>
       <c r="R32" t="n">
-        <v>6626394</v>
+        <v>6626277</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3727,6 +3731,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3745,32 +3750,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985883</v>
+        <v>128985893</v>
       </c>
       <c r="B33" t="n">
-        <v>89415</v>
+        <v>58582</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>37</v>
+        <v>208249</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720621</v>
+        <v>720574</v>
       </c>
       <c r="R33" t="n">
-        <v>6626429</v>
+        <v>6626394</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3816,11 +3821,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>92443</v>
+        <v>86944</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R34" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985859</v>
+        <v>128985852</v>
       </c>
       <c r="B35" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,34 +3955,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720718</v>
+        <v>720548</v>
       </c>
       <c r="R35" t="n">
-        <v>6626247</v>
+        <v>6626285</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4023,6 +4026,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4041,10 +4045,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985908</v>
+        <v>128985889</v>
       </c>
       <c r="B36" t="n">
-        <v>86939</v>
+        <v>92839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4052,34 +4056,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720504</v>
+        <v>720564</v>
       </c>
       <c r="R36" t="n">
-        <v>6626377</v>
+        <v>6626459</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4120,6 +4127,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4138,10 +4146,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985852</v>
+        <v>128985879</v>
       </c>
       <c r="B37" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720548</v>
+        <v>720754</v>
       </c>
       <c r="R37" t="n">
-        <v>6626285</v>
+        <v>6626384</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4239,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985889</v>
+        <v>128985876</v>
       </c>
       <c r="B38" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4250,37 +4258,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720564</v>
+        <v>720766</v>
       </c>
       <c r="R38" t="n">
-        <v>6626459</v>
+        <v>6626378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4321,7 +4326,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985879</v>
+        <v>128985859</v>
       </c>
       <c r="B39" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4351,37 +4355,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720754</v>
+        <v>720718</v>
       </c>
       <c r="R39" t="n">
-        <v>6626384</v>
+        <v>6626247</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4422,7 +4423,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B43" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4751,37 +4751,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R43" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4822,7 +4819,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4841,10 +4837,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B44" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R44" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4942,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B45" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4953,34 +4949,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R45" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5021,6 +5020,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5039,32 +5039,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B46" t="n">
-        <v>58577</v>
+        <v>86860</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R46" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B47" t="n">
-        <v>86855</v>
+        <v>91882</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5147,34 +5147,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R47" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5209,6 +5212,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5217,6 +5225,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5233,48 +5261,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985882</v>
+        <v>128985899</v>
       </c>
       <c r="B48" t="n">
-        <v>91877</v>
+        <v>58580</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1506</v>
+        <v>208250</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720643</v>
+        <v>720542</v>
       </c>
       <c r="R48" t="n">
-        <v>6626413</v>
+        <v>6626391</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5309,11 +5334,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5322,26 +5342,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,45 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92829</v>
+        <v>92847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R6" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1151,6 +1154,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,48 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>92829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R7" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1251,7 +1252,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985861</v>
+        <v>128985887</v>
       </c>
       <c r="B19" t="n">
-        <v>92847</v>
+        <v>105701</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2368,37 +2368,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>224098</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720733</v>
+        <v>720586</v>
       </c>
       <c r="R19" t="n">
-        <v>6626258</v>
+        <v>6626407</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,7 +2436,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2458,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B20" t="n">
-        <v>105701</v>
+        <v>92847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2469,34 +2465,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R20" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2537,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3547,48 +3547,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985865</v>
+        <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>92847</v>
+        <v>89427</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720780</v>
+        <v>720621</v>
       </c>
       <c r="R31" t="n">
-        <v>6626277</v>
+        <v>6626429</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3623,13 +3620,17 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3648,45 +3649,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>89427</v>
+        <v>92847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R32" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3721,17 +3725,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985852</v>
+        <v>128985876</v>
       </c>
       <c r="B34" t="n">
-        <v>92847</v>
+        <v>92456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,37 +3858,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720548</v>
+        <v>720766</v>
       </c>
       <c r="R34" t="n">
-        <v>6626285</v>
+        <v>6626378</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3929,7 +3926,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3948,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985889</v>
+        <v>128985859</v>
       </c>
       <c r="B35" t="n">
-        <v>92847</v>
+        <v>92456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3959,37 +3955,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720564</v>
+        <v>720718</v>
       </c>
       <c r="R35" t="n">
-        <v>6626459</v>
+        <v>6626247</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4030,7 +4023,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4049,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985908</v>
+        <v>128985879</v>
       </c>
       <c r="B36" t="n">
-        <v>86951</v>
+        <v>92847</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4060,34 +4052,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720504</v>
+        <v>720754</v>
       </c>
       <c r="R36" t="n">
-        <v>6626377</v>
+        <v>6626384</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4128,6 +4123,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4142,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B37" t="n">
-        <v>92456</v>
+        <v>86951</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4157,21 +4153,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4181,10 +4177,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R37" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4243,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985859</v>
+        <v>128985852</v>
       </c>
       <c r="B38" t="n">
-        <v>92456</v>
+        <v>92847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4254,34 +4250,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720718</v>
+        <v>720548</v>
       </c>
       <c r="R38" t="n">
-        <v>6626247</v>
+        <v>6626285</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4322,6 +4321,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985879</v>
+        <v>128985889</v>
       </c>
       <c r="B39" t="n">
         <v>92847</v>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720754</v>
+        <v>720564</v>
       </c>
       <c r="R39" t="n">
-        <v>6626384</v>
+        <v>6626459</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4740,45 +4740,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985902</v>
+        <v>128985882</v>
       </c>
       <c r="B43" t="n">
-        <v>92456</v>
+        <v>91890</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>1506</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720521</v>
+        <v>720643</v>
       </c>
       <c r="R43" t="n">
-        <v>6626387</v>
+        <v>6626413</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4813,6 +4816,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4821,6 +4829,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4934,48 +4962,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B45" t="n">
-        <v>91890</v>
+        <v>92456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R45" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5010,11 +5035,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5023,26 +5043,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,48 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92847</v>
+        <v>92834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R6" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1154,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,45 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92829</v>
+        <v>92852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R7" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1252,6 +1251,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>98673</v>
+        <v>92852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R8" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1349,6 +1352,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R9" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,37 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R10" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1550,7 +1551,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R11" t="n">
         <v>6626397</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R12" t="n">
         <v>6626397</v>
@@ -1766,7 +1766,7 @@
         <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B17" t="n">
-        <v>92150</v>
+        <v>91735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R17" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985860</v>
+        <v>128985866</v>
       </c>
       <c r="B18" t="n">
-        <v>91732</v>
+        <v>92155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720709</v>
+        <v>720790</v>
       </c>
       <c r="R18" t="n">
-        <v>6626266</v>
+        <v>6626254</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B19" t="n">
-        <v>105701</v>
+        <v>92852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2368,34 +2368,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R19" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2436,6 +2439,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2454,10 +2458,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985861</v>
+        <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>92847</v>
+        <v>105706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2469,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>224098</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720733</v>
+        <v>720586</v>
       </c>
       <c r="R20" t="n">
-        <v>6626258</v>
+        <v>6626407</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2537,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>128985850</v>
       </c>
       <c r="B21" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985890</v>
       </c>
       <c r="B22" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>89427</v>
+        <v>89430</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985876</v>
+        <v>128985852</v>
       </c>
       <c r="B34" t="n">
-        <v>92456</v>
+        <v>92852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,34 +3858,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720766</v>
+        <v>720548</v>
       </c>
       <c r="R34" t="n">
-        <v>6626378</v>
+        <v>6626285</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3926,6 +3929,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3944,10 +3948,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985859</v>
+        <v>128985889</v>
       </c>
       <c r="B35" t="n">
-        <v>92456</v>
+        <v>92852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,34 +3959,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720718</v>
+        <v>720564</v>
       </c>
       <c r="R35" t="n">
-        <v>6626247</v>
+        <v>6626459</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4023,6 +4030,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4052,7 @@
         <v>128985879</v>
       </c>
       <c r="B36" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4142,10 +4150,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B37" t="n">
-        <v>86951</v>
+        <v>92461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4153,21 +4161,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4177,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R37" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4239,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985852</v>
+        <v>128985859</v>
       </c>
       <c r="B38" t="n">
-        <v>92847</v>
+        <v>92461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4250,37 +4258,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720548</v>
+        <v>720718</v>
       </c>
       <c r="R38" t="n">
-        <v>6626285</v>
+        <v>6626247</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4321,7 +4326,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985889</v>
+        <v>128985908</v>
       </c>
       <c r="B39" t="n">
-        <v>92847</v>
+        <v>86954</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4351,37 +4355,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720564</v>
+        <v>720504</v>
       </c>
       <c r="R39" t="n">
-        <v>6626459</v>
+        <v>6626377</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4422,7 +4423,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>128985885</v>
       </c>
       <c r="B40" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>128985895</v>
       </c>
       <c r="B41" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128985906</v>
       </c>
       <c r="B42" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B43" t="n">
-        <v>91890</v>
+        <v>92852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R43" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4816,39 +4816,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4868,7 +4844,7 @@
         <v>128985873</v>
       </c>
       <c r="B44" t="n">
-        <v>86867</v>
+        <v>86870</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4965,7 +4941,7 @@
         <v>128985902</v>
       </c>
       <c r="B45" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,32 +5035,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985896</v>
+        <v>128985882</v>
       </c>
       <c r="B46" t="n">
-        <v>92847</v>
+        <v>91893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5097,10 +5073,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720577</v>
+        <v>720643</v>
       </c>
       <c r="R46" t="n">
-        <v>6626370</v>
+        <v>6626413</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5135,15 +5111,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5160,10 +5160,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B47" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R47" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,45 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R6" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1151,6 +1154,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,48 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92852</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R7" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1251,7 +1252,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>128985905</v>
       </c>
       <c r="B9" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985854</v>
+        <v>128985888</v>
       </c>
       <c r="B13" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720559</v>
+        <v>720578</v>
       </c>
       <c r="R13" t="n">
-        <v>6626267</v>
+        <v>6626426</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985888</v>
+        <v>128985854</v>
       </c>
       <c r="B14" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720578</v>
+        <v>720559</v>
       </c>
       <c r="R14" t="n">
-        <v>6626426</v>
+        <v>6626267</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1965,48 +1965,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92852</v>
+        <v>92808</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2044,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92805</v>
+        <v>92855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985860</v>
+        <v>128985866</v>
       </c>
       <c r="B17" t="n">
-        <v>91735</v>
+        <v>92158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720709</v>
+        <v>720790</v>
       </c>
       <c r="R17" t="n">
-        <v>6626266</v>
+        <v>6626254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B18" t="n">
-        <v>92155</v>
+        <v>91738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R18" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2360,7 +2360,7 @@
         <v>128985861</v>
       </c>
       <c r="B19" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>105706</v>
+        <v>105709</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128985850</v>
       </c>
       <c r="B21" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985890</v>
       </c>
       <c r="B22" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B24" t="n">
-        <v>92828</v>
+        <v>91035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R24" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B25" t="n">
-        <v>91032</v>
+        <v>92831</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R25" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>128985891</v>
       </c>
       <c r="B27" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>89430</v>
+        <v>89433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985865</v>
+        <v>128985893</v>
       </c>
       <c r="B32" t="n">
-        <v>92852</v>
+        <v>58582</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,37 +3660,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720780</v>
+        <v>720574</v>
       </c>
       <c r="R32" t="n">
-        <v>6626277</v>
+        <v>6626394</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3731,7 +3728,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3750,10 +3746,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985893</v>
+        <v>128985865</v>
       </c>
       <c r="B33" t="n">
-        <v>58582</v>
+        <v>92855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3761,34 +3757,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208249</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720574</v>
+        <v>720780</v>
       </c>
       <c r="R33" t="n">
-        <v>6626394</v>
+        <v>6626277</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3829,6 +3828,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985852</v>
+        <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>92852</v>
+        <v>86957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,37 +3858,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720548</v>
+        <v>720504</v>
       </c>
       <c r="R34" t="n">
-        <v>6626285</v>
+        <v>6626377</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3929,7 +3926,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3948,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985889</v>
+        <v>128985852</v>
       </c>
       <c r="B35" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3986,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720564</v>
+        <v>720548</v>
       </c>
       <c r="R35" t="n">
-        <v>6626459</v>
+        <v>6626285</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4049,10 +4045,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985879</v>
+        <v>128985889</v>
       </c>
       <c r="B36" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4087,10 +4083,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720754</v>
+        <v>720564</v>
       </c>
       <c r="R36" t="n">
-        <v>6626384</v>
+        <v>6626459</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4150,10 +4146,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B37" t="n">
-        <v>92461</v>
+        <v>92855</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4161,34 +4157,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R37" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,6 +4228,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985859</v>
+        <v>128985876</v>
       </c>
       <c r="B38" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720718</v>
+        <v>720766</v>
       </c>
       <c r="R38" t="n">
-        <v>6626247</v>
+        <v>6626378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985908</v>
+        <v>128985859</v>
       </c>
       <c r="B39" t="n">
-        <v>86954</v>
+        <v>92464</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4355,21 +4355,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720504</v>
+        <v>720718</v>
       </c>
       <c r="R39" t="n">
-        <v>6626377</v>
+        <v>6626247</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4444,7 +4444,7 @@
         <v>128985885</v>
       </c>
       <c r="B40" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>128985895</v>
       </c>
       <c r="B41" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128985906</v>
       </c>
       <c r="B42" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B43" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R43" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4841,45 +4841,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B44" t="n">
-        <v>86870</v>
+        <v>92855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R44" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4920,6 +4923,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4938,45 +4942,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985902</v>
+        <v>128985882</v>
       </c>
       <c r="B45" t="n">
-        <v>92461</v>
+        <v>91896</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>1506</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720521</v>
+        <v>720643</v>
       </c>
       <c r="R45" t="n">
-        <v>6626387</v>
+        <v>6626413</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5011,6 +5018,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5019,6 +5031,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5035,10 +5067,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985882</v>
+        <v>128985873</v>
       </c>
       <c r="B46" t="n">
-        <v>91893</v>
+        <v>86873</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,37 +5078,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>445</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720643</v>
+        <v>720771</v>
       </c>
       <c r="R46" t="n">
-        <v>6626413</v>
+        <v>6626378</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5111,11 +5140,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5124,26 +5148,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5160,10 +5164,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B47" t="n">
-        <v>92852</v>
+        <v>92464</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5171,37 +5175,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R47" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5242,7 +5243,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,48 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92855</v>
+        <v>92837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R6" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1154,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,45 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92837</v>
+        <v>92855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R7" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1252,6 +1251,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B11" t="n">
         <v>92464</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R11" t="n">
         <v>6626397</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B12" t="n">
         <v>92464</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R12" t="n">
         <v>6626397</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985888</v>
+        <v>128985854</v>
       </c>
       <c r="B13" t="n">
         <v>92855</v>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720578</v>
+        <v>720559</v>
       </c>
       <c r="R13" t="n">
-        <v>6626426</v>
+        <v>6626267</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985854</v>
+        <v>128985888</v>
       </c>
       <c r="B14" t="n">
         <v>92855</v>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720559</v>
+        <v>720578</v>
       </c>
       <c r="R14" t="n">
-        <v>6626267</v>
+        <v>6626426</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985850</v>
+        <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>92464</v>
+        <v>86882</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720528</v>
+        <v>720530</v>
       </c>
       <c r="R21" t="n">
-        <v>6626273</v>
+        <v>6626415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985890</v>
+        <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>86882</v>
+        <v>92464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3611</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720530</v>
+        <v>720528</v>
       </c>
       <c r="R22" t="n">
-        <v>6626415</v>
+        <v>6626273</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B28" t="n">
-        <v>92808</v>
+        <v>91299</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R28" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>92808</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R29" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3547,45 +3547,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B31" t="n">
-        <v>89433</v>
+        <v>92855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R31" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3620,17 +3623,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3649,32 +3648,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985893</v>
+        <v>128985883</v>
       </c>
       <c r="B32" t="n">
-        <v>58582</v>
+        <v>89433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208249</v>
+        <v>37</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3684,10 +3683,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720574</v>
+        <v>720621</v>
       </c>
       <c r="R32" t="n">
-        <v>6626394</v>
+        <v>6626429</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3720,6 +3719,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3746,10 +3750,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985865</v>
+        <v>128985893</v>
       </c>
       <c r="B33" t="n">
-        <v>92855</v>
+        <v>58582</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3757,37 +3761,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720780</v>
+        <v>720574</v>
       </c>
       <c r="R33" t="n">
-        <v>6626277</v>
+        <v>6626394</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3828,7 +3829,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B34" t="n">
-        <v>86957</v>
+        <v>92464</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R34" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985852</v>
+        <v>128985859</v>
       </c>
       <c r="B35" t="n">
-        <v>92855</v>
+        <v>92464</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,37 +3955,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720548</v>
+        <v>720718</v>
       </c>
       <c r="R35" t="n">
-        <v>6626285</v>
+        <v>6626247</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4026,7 +4023,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4045,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985889</v>
+        <v>128985908</v>
       </c>
       <c r="B36" t="n">
-        <v>92855</v>
+        <v>86957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4056,37 +4052,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720564</v>
+        <v>720504</v>
       </c>
       <c r="R36" t="n">
-        <v>6626459</v>
+        <v>6626377</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4127,7 +4120,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4146,7 +4138,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985879</v>
+        <v>128985852</v>
       </c>
       <c r="B37" t="n">
         <v>92855</v>
@@ -4184,10 +4176,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720754</v>
+        <v>720548</v>
       </c>
       <c r="R37" t="n">
-        <v>6626384</v>
+        <v>6626285</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4247,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985876</v>
+        <v>128985889</v>
       </c>
       <c r="B38" t="n">
-        <v>92464</v>
+        <v>92855</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4258,34 +4250,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720766</v>
+        <v>720564</v>
       </c>
       <c r="R38" t="n">
-        <v>6626378</v>
+        <v>6626459</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4326,6 +4321,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4344,10 +4340,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985859</v>
+        <v>128985879</v>
       </c>
       <c r="B39" t="n">
-        <v>92464</v>
+        <v>92855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4355,34 +4351,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720718</v>
+        <v>720754</v>
       </c>
       <c r="R39" t="n">
-        <v>6626247</v>
+        <v>6626384</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4423,6 +4422,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4441,48 +4441,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128985885</v>
+        <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92855</v>
+        <v>92808</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720573</v>
+        <v>720486</v>
       </c>
       <c r="R40" t="n">
-        <v>6626380</v>
+        <v>6626330</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4523,7 +4520,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4542,7 +4538,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128985895</v>
+        <v>128985885</v>
       </c>
       <c r="B41" t="n">
         <v>92855</v>
@@ -4580,10 +4576,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720572</v>
+        <v>720573</v>
       </c>
       <c r="R41" t="n">
-        <v>6626395</v>
+        <v>6626380</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4643,45 +4639,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128985906</v>
+        <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92808</v>
+        <v>92855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720486</v>
+        <v>720572</v>
       </c>
       <c r="R42" t="n">
-        <v>6626330</v>
+        <v>6626395</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4722,6 +4721,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4942,48 +4942,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B45" t="n">
-        <v>91896</v>
+        <v>92464</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R45" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5018,11 +5015,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5031,26 +5023,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5164,45 +5136,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985902</v>
+        <v>128985882</v>
       </c>
       <c r="B47" t="n">
-        <v>92464</v>
+        <v>91896</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>1506</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720521</v>
+        <v>720643</v>
       </c>
       <c r="R47" t="n">
-        <v>6626387</v>
+        <v>6626413</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5237,6 +5212,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5245,6 +5225,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -3547,48 +3547,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985865</v>
+        <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>92855</v>
+        <v>89433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720780</v>
+        <v>720621</v>
       </c>
       <c r="R31" t="n">
-        <v>6626277</v>
+        <v>6626429</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3623,13 +3620,17 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3648,45 +3649,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>89433</v>
+        <v>92855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R32" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3721,17 +3725,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B43" t="n">
-        <v>92855</v>
+        <v>92464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4751,37 +4751,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R43" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4822,7 +4819,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4841,7 +4837,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B44" t="n">
         <v>92855</v>
@@ -4879,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R44" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4942,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B45" t="n">
-        <v>92464</v>
+        <v>92855</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4953,34 +4949,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R45" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5021,6 +5020,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,45 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92837</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R6" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1151,6 +1154,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,48 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92855</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R7" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1251,7 +1252,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B8" t="n">
-        <v>92855</v>
+        <v>98681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,37 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R8" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1352,7 +1349,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,7 +1367,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985905</v>
+        <v>128985897</v>
       </c>
       <c r="B9" t="n">
         <v>92855</v>
@@ -1409,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720491</v>
+        <v>720543</v>
       </c>
       <c r="R9" t="n">
-        <v>6626322</v>
+        <v>6626360</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985884</v>
+        <v>128985905</v>
       </c>
       <c r="B10" t="n">
-        <v>98681</v>
+        <v>92855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,34 +1479,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720568</v>
+        <v>720491</v>
       </c>
       <c r="R10" t="n">
-        <v>6626387</v>
+        <v>6626322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1551,6 +1550,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B11" t="n">
         <v>92464</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R11" t="n">
         <v>6626397</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B12" t="n">
         <v>92464</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R12" t="n">
         <v>6626397</v>
@@ -1965,45 +1965,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92808</v>
+        <v>92855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R15" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2062,48 +2066,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92855</v>
+        <v>92808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R16" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2144,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>91738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R17" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985860</v>
+        <v>128985866</v>
       </c>
       <c r="B18" t="n">
-        <v>91738</v>
+        <v>92158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720709</v>
+        <v>720790</v>
       </c>
       <c r="R18" t="n">
-        <v>6626266</v>
+        <v>6626254</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>91035</v>
+        <v>92831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R24" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>92831</v>
+        <v>91035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R25" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>92808</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R28" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>92808</v>
+        <v>91299</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R29" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985908</v>
+        <v>128985852</v>
       </c>
       <c r="B36" t="n">
-        <v>86957</v>
+        <v>92855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4052,34 +4052,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720504</v>
+        <v>720548</v>
       </c>
       <c r="R36" t="n">
-        <v>6626377</v>
+        <v>6626285</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4120,6 +4123,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4138,7 +4142,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985852</v>
+        <v>128985889</v>
       </c>
       <c r="B37" t="n">
         <v>92855</v>
@@ -4176,10 +4180,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720548</v>
+        <v>720564</v>
       </c>
       <c r="R37" t="n">
-        <v>6626285</v>
+        <v>6626459</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4239,7 +4243,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985889</v>
+        <v>128985879</v>
       </c>
       <c r="B38" t="n">
         <v>92855</v>
@@ -4277,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720564</v>
+        <v>720754</v>
       </c>
       <c r="R38" t="n">
-        <v>6626459</v>
+        <v>6626384</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B39" t="n">
-        <v>92855</v>
+        <v>86957</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4351,37 +4355,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R39" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4422,7 +4423,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B43" t="n">
-        <v>92464</v>
+        <v>86873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R43" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B46" t="n">
-        <v>86873</v>
+        <v>91896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5050,34 +5050,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R46" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5112,6 +5115,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5120,6 +5128,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5136,48 +5164,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B47" t="n">
-        <v>91896</v>
+        <v>92464</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R47" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5212,11 +5237,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5225,26 +5245,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,48 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92855</v>
+        <v>92844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R6" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1154,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,45 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92837</v>
+        <v>92862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R7" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1252,6 +1251,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>128985884</v>
       </c>
       <c r="B8" t="n">
-        <v>98681</v>
+        <v>98691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>128985897</v>
       </c>
       <c r="B9" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>128985905</v>
       </c>
       <c r="B10" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,48 +1965,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92855</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2044,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92808</v>
+        <v>92862</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985860</v>
+        <v>128985866</v>
       </c>
       <c r="B17" t="n">
-        <v>91738</v>
+        <v>92165</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720709</v>
+        <v>720790</v>
       </c>
       <c r="R17" t="n">
-        <v>6626266</v>
+        <v>6626254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B18" t="n">
-        <v>92158</v>
+        <v>91745</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R18" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2360,7 +2360,7 @@
         <v>128985861</v>
       </c>
       <c r="B19" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>105709</v>
+        <v>105719</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>128985891</v>
       </c>
       <c r="B27" t="n">
-        <v>79415</v>
+        <v>79419</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B28" t="n">
-        <v>92808</v>
+        <v>91305</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R28" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>92815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R29" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>89433</v>
+        <v>89437</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128985893</v>
       </c>
       <c r="B33" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>92464</v>
+        <v>86961</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R34" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985859</v>
+        <v>128985876</v>
       </c>
       <c r="B35" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720718</v>
+        <v>720766</v>
       </c>
       <c r="R35" t="n">
-        <v>6626247</v>
+        <v>6626378</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985852</v>
+        <v>128985859</v>
       </c>
       <c r="B36" t="n">
-        <v>92855</v>
+        <v>92471</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4052,37 +4052,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720548</v>
+        <v>720718</v>
       </c>
       <c r="R36" t="n">
-        <v>6626285</v>
+        <v>6626247</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4123,7 +4120,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4142,10 +4138,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985889</v>
+        <v>128985852</v>
       </c>
       <c r="B37" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4180,10 +4176,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720564</v>
+        <v>720548</v>
       </c>
       <c r="R37" t="n">
-        <v>6626459</v>
+        <v>6626285</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4243,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985879</v>
+        <v>128985889</v>
       </c>
       <c r="B38" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4281,10 +4277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720754</v>
+        <v>720564</v>
       </c>
       <c r="R38" t="n">
-        <v>6626384</v>
+        <v>6626459</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4344,10 +4340,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985908</v>
+        <v>128985879</v>
       </c>
       <c r="B39" t="n">
-        <v>86957</v>
+        <v>92862</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4355,34 +4351,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720504</v>
+        <v>720754</v>
       </c>
       <c r="R39" t="n">
-        <v>6626377</v>
+        <v>6626384</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4423,6 +4422,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4441,45 +4441,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128985906</v>
+        <v>128985885</v>
       </c>
       <c r="B40" t="n">
-        <v>92808</v>
+        <v>92862</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720486</v>
+        <v>720573</v>
       </c>
       <c r="R40" t="n">
-        <v>6626330</v>
+        <v>6626380</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4520,6 +4523,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4538,10 +4542,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128985885</v>
+        <v>128985895</v>
       </c>
       <c r="B41" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4576,10 +4580,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720573</v>
+        <v>720572</v>
       </c>
       <c r="R41" t="n">
-        <v>6626380</v>
+        <v>6626395</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4639,48 +4643,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128985895</v>
+        <v>128985906</v>
       </c>
       <c r="B42" t="n">
-        <v>92855</v>
+        <v>92815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720572</v>
+        <v>720486</v>
       </c>
       <c r="R42" t="n">
-        <v>6626395</v>
+        <v>6626330</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4721,7 +4722,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B43" t="n">
-        <v>86873</v>
+        <v>91903</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4751,34 +4751,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R43" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4813,6 +4816,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4821,6 +4829,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4837,10 +4865,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B44" t="n">
-        <v>92855</v>
+        <v>92471</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4848,37 +4876,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R44" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4919,7 +4944,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4938,10 +4962,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B45" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4976,10 +5000,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R45" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5039,32 +5063,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B46" t="n">
-        <v>91896</v>
+        <v>92862</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5077,10 +5101,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R46" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5115,39 +5139,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5164,10 +5164,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985902</v>
+        <v>128985899</v>
       </c>
       <c r="B47" t="n">
-        <v>92464</v>
+        <v>58582</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,21 +5175,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>208250</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720521</v>
+        <v>720542</v>
       </c>
       <c r="R47" t="n">
-        <v>6626387</v>
+        <v>6626391</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B48" t="n">
-        <v>58580</v>
+        <v>86877</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R48" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>98691</v>
+        <v>92862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R8" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1349,6 +1352,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1367,7 +1371,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B9" t="n">
         <v>92862</v>
@@ -1405,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R9" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>92862</v>
+        <v>98691</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,37 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R10" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1550,7 +1551,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1965,45 +1965,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92815</v>
+        <v>92862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R15" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2062,48 +2066,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92862</v>
+        <v>92815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R16" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2144,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92844</v>
+        <v>92851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B8" t="n">
-        <v>92862</v>
+        <v>98698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,37 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R8" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1352,7 +1349,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985905</v>
+        <v>128985897</v>
       </c>
       <c r="B9" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720491</v>
+        <v>720543</v>
       </c>
       <c r="R9" t="n">
-        <v>6626322</v>
+        <v>6626360</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985884</v>
+        <v>128985905</v>
       </c>
       <c r="B10" t="n">
-        <v>98691</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,34 +1479,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720568</v>
+        <v>720491</v>
       </c>
       <c r="R10" t="n">
-        <v>6626387</v>
+        <v>6626322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1551,6 +1550,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985900</v>
+        <v>128985854</v>
       </c>
       <c r="B11" t="n">
-        <v>92471</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,34 +1580,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720544</v>
+        <v>720559</v>
       </c>
       <c r="R11" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1648,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B12" t="n">
-        <v>92471</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1677,34 +1681,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R12" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1745,6 +1752,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1763,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B13" t="n">
-        <v>92862</v>
+        <v>92478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1774,37 +1782,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R13" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1845,7 +1850,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B14" t="n">
-        <v>92862</v>
+        <v>92478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,37 +1879,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R14" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1946,7 +1947,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,48 +1965,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92862</v>
+        <v>92822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2044,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92815</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985866</v>
+        <v>128985861</v>
       </c>
       <c r="B17" t="n">
-        <v>92165</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,34 +2174,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720790</v>
+        <v>720733</v>
       </c>
       <c r="R17" t="n">
-        <v>6626254</v>
+        <v>6626258</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,6 +2245,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2260,32 +2264,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985860</v>
+        <v>128985866</v>
       </c>
       <c r="B18" t="n">
-        <v>91745</v>
+        <v>92172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720709</v>
+        <v>720790</v>
       </c>
       <c r="R18" t="n">
-        <v>6626266</v>
+        <v>6626254</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2357,48 +2361,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985861</v>
+        <v>128985860</v>
       </c>
       <c r="B19" t="n">
-        <v>92862</v>
+        <v>91752</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>1106</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720733</v>
+        <v>720709</v>
       </c>
       <c r="R19" t="n">
-        <v>6626258</v>
+        <v>6626266</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,7 +2440,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>105719</v>
+        <v>105726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985890</v>
+        <v>128985850</v>
       </c>
       <c r="B21" t="n">
-        <v>86886</v>
+        <v>92478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3611</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720530</v>
+        <v>720528</v>
       </c>
       <c r="R21" t="n">
-        <v>6626415</v>
+        <v>6626273</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985850</v>
+        <v>128985890</v>
       </c>
       <c r="B22" t="n">
-        <v>92471</v>
+        <v>86893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720528</v>
+        <v>720530</v>
       </c>
       <c r="R22" t="n">
-        <v>6626273</v>
+        <v>6626415</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B24" t="n">
-        <v>92838</v>
+        <v>91046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R24" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B25" t="n">
-        <v>91039</v>
+        <v>92845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R25" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>91305</v>
+        <v>92822</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R28" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>92815</v>
+        <v>91312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R29" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>89437</v>
+        <v>89444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985876</v>
+        <v>128985889</v>
       </c>
       <c r="B35" t="n">
-        <v>92471</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,34 +3955,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720766</v>
+        <v>720564</v>
       </c>
       <c r="R35" t="n">
-        <v>6626378</v>
+        <v>6626459</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4023,6 +4026,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4041,10 +4045,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985859</v>
+        <v>128985876</v>
       </c>
       <c r="B36" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4076,10 +4080,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720718</v>
+        <v>720766</v>
       </c>
       <c r="R36" t="n">
-        <v>6626247</v>
+        <v>6626378</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4138,10 +4142,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985852</v>
+        <v>128985859</v>
       </c>
       <c r="B37" t="n">
-        <v>92862</v>
+        <v>92478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4149,37 +4153,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720548</v>
+        <v>720718</v>
       </c>
       <c r="R37" t="n">
-        <v>6626285</v>
+        <v>6626247</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4220,7 +4221,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985889</v>
+        <v>128985852</v>
       </c>
       <c r="B38" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720564</v>
+        <v>720548</v>
       </c>
       <c r="R38" t="n">
-        <v>6626459</v>
+        <v>6626285</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4343,7 +4343,7 @@
         <v>128985879</v>
       </c>
       <c r="B39" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4441,48 +4441,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128985885</v>
+        <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92862</v>
+        <v>92822</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720573</v>
+        <v>720486</v>
       </c>
       <c r="R40" t="n">
-        <v>6626380</v>
+        <v>6626330</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4523,7 +4520,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4542,10 +4538,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128985895</v>
+        <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,10 +4576,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720572</v>
+        <v>720573</v>
       </c>
       <c r="R41" t="n">
-        <v>6626395</v>
+        <v>6626380</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4643,45 +4639,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128985906</v>
+        <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92815</v>
+        <v>92869</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720486</v>
+        <v>720572</v>
       </c>
       <c r="R42" t="n">
-        <v>6626330</v>
+        <v>6626395</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4722,6 +4721,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>128985882</v>
       </c>
       <c r="B43" t="n">
-        <v>91903</v>
+        <v>91910</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,32 +4865,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B44" t="n">
-        <v>92471</v>
+        <v>86884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R44" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4965,7 +4965,7 @@
         <v>128985896</v>
       </c>
       <c r="B45" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>128985875</v>
       </c>
       <c r="B46" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985899</v>
+        <v>128985902</v>
       </c>
       <c r="B47" t="n">
-        <v>58582</v>
+        <v>92478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,21 +5175,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>208250</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720542</v>
+        <v>720521</v>
       </c>
       <c r="R47" t="n">
-        <v>6626391</v>
+        <v>6626387</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985873</v>
+        <v>128985899</v>
       </c>
       <c r="B48" t="n">
-        <v>86877</v>
+        <v>58582</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>445</v>
+        <v>208250</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720771</v>
+        <v>720542</v>
       </c>
       <c r="R48" t="n">
-        <v>6626378</v>
+        <v>6626391</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,45 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92851</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R6" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1151,6 +1154,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,48 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R7" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1251,7 +1252,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>98698</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R8" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1349,6 +1352,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R9" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>98700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,37 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R10" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1550,7 +1551,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,37 +1580,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R11" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1651,7 +1648,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1666,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>92480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,37 +1677,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R12" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1752,7 +1745,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1771,10 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985900</v>
+        <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92478</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,34 +1774,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720544</v>
+        <v>720559</v>
       </c>
       <c r="R13" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1850,6 +1845,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1868,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92478</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,34 +1875,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R14" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1947,6 +1946,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,45 +1965,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92822</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R15" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2062,48 +2066,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>92824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R16" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2144,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985861</v>
+        <v>128985866</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,37 +2174,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720733</v>
+        <v>720790</v>
       </c>
       <c r="R17" t="n">
-        <v>6626258</v>
+        <v>6626254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2245,7 +2242,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2264,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985866</v>
+        <v>128985861</v>
       </c>
       <c r="B18" t="n">
-        <v>92172</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2275,34 +2271,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720790</v>
+        <v>720733</v>
       </c>
       <c r="R18" t="n">
-        <v>6626254</v>
+        <v>6626258</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2343,6 +2342,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>128985860</v>
       </c>
       <c r="B19" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>105726</v>
+        <v>105728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>128985850</v>
       </c>
       <c r="B21" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985890</v>
       </c>
       <c r="B22" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>91046</v>
+        <v>92847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R24" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>92845</v>
+        <v>91048</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R25" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>128985891</v>
       </c>
       <c r="B27" t="n">
-        <v>79419</v>
+        <v>79421</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>92822</v>
+        <v>92824</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>89444</v>
+        <v>89446</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>128985893</v>
       </c>
       <c r="B33" t="n">
-        <v>58584</v>
+        <v>58586</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985889</v>
+        <v>128985876</v>
       </c>
       <c r="B35" t="n">
-        <v>92869</v>
+        <v>92480</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,37 +3955,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720564</v>
+        <v>720766</v>
       </c>
       <c r="R35" t="n">
-        <v>6626459</v>
+        <v>6626378</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4026,7 +4023,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4045,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985876</v>
+        <v>128985859</v>
       </c>
       <c r="B36" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4080,10 +4076,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720766</v>
+        <v>720718</v>
       </c>
       <c r="R36" t="n">
-        <v>6626378</v>
+        <v>6626247</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4142,10 +4138,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985859</v>
+        <v>128985852</v>
       </c>
       <c r="B37" t="n">
-        <v>92478</v>
+        <v>92871</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4153,34 +4149,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720718</v>
+        <v>720548</v>
       </c>
       <c r="R37" t="n">
-        <v>6626247</v>
+        <v>6626285</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4221,6 +4220,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985852</v>
+        <v>128985889</v>
       </c>
       <c r="B38" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720548</v>
+        <v>720564</v>
       </c>
       <c r="R38" t="n">
-        <v>6626285</v>
+        <v>6626459</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4343,7 +4343,7 @@
         <v>128985879</v>
       </c>
       <c r="B39" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92822</v>
+        <v>92824</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985882</v>
+        <v>128985896</v>
       </c>
       <c r="B43" t="n">
-        <v>91910</v>
+        <v>92871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720643</v>
+        <v>720577</v>
       </c>
       <c r="R43" t="n">
-        <v>6626413</v>
+        <v>6626370</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4816,39 +4816,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4865,45 +4841,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B44" t="n">
-        <v>86884</v>
+        <v>92871</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R44" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4944,6 +4923,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4962,10 +4942,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985896</v>
+        <v>128985899</v>
       </c>
       <c r="B45" t="n">
-        <v>92869</v>
+        <v>58584</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4973,37 +4953,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720577</v>
+        <v>720542</v>
       </c>
       <c r="R45" t="n">
-        <v>6626370</v>
+        <v>6626391</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5044,7 +5021,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5063,32 +5039,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B46" t="n">
-        <v>92869</v>
+        <v>91912</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5101,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R46" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5139,15 +5115,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5167,7 +5167,7 @@
         <v>128985902</v>
       </c>
       <c r="B47" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B48" t="n">
-        <v>58582</v>
+        <v>86886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R48" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,48 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>92853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R6" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1154,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,45 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92853</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R7" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1252,6 +1251,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1965,48 +1965,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>92824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2044,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92824</v>
+        <v>92871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B17" t="n">
-        <v>92174</v>
+        <v>91754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R17" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985861</v>
+        <v>128985866</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,37 +2271,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720733</v>
+        <v>720790</v>
       </c>
       <c r="R18" t="n">
-        <v>6626258</v>
+        <v>6626254</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2342,7 +2339,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2361,45 +2357,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985860</v>
+        <v>128985861</v>
       </c>
       <c r="B19" t="n">
-        <v>91754</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1106</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720709</v>
+        <v>720733</v>
       </c>
       <c r="R19" t="n">
-        <v>6626266</v>
+        <v>6626258</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2440,6 +2439,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985883</v>
+        <v>128985893</v>
       </c>
       <c r="B31" t="n">
-        <v>89446</v>
+        <v>58586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>208249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720621</v>
+        <v>720574</v>
       </c>
       <c r="R31" t="n">
-        <v>6626429</v>
+        <v>6626394</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3618,11 +3618,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3750,32 +3745,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985893</v>
+        <v>128985883</v>
       </c>
       <c r="B33" t="n">
-        <v>58586</v>
+        <v>89446</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208249</v>
+        <v>37</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720574</v>
+        <v>720621</v>
       </c>
       <c r="R33" t="n">
-        <v>6626394</v>
+        <v>6626429</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3821,6 +3816,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B34" t="n">
-        <v>86970</v>
+        <v>92480</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R34" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985876</v>
+        <v>128985859</v>
       </c>
       <c r="B35" t="n">
         <v>92480</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720766</v>
+        <v>720718</v>
       </c>
       <c r="R35" t="n">
-        <v>6626378</v>
+        <v>6626247</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985859</v>
+        <v>128985908</v>
       </c>
       <c r="B36" t="n">
-        <v>92480</v>
+        <v>86970</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720718</v>
+        <v>720504</v>
       </c>
       <c r="R36" t="n">
-        <v>6626247</v>
+        <v>6626377</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B43" t="n">
-        <v>92871</v>
+        <v>92480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4751,37 +4751,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R43" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4822,7 +4819,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4841,10 +4837,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985875</v>
+        <v>128985899</v>
       </c>
       <c r="B44" t="n">
-        <v>92871</v>
+        <v>58584</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4852,37 +4848,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720769</v>
+        <v>720542</v>
       </c>
       <c r="R44" t="n">
-        <v>6626395</v>
+        <v>6626391</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4923,7 +4916,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4942,32 +4934,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B45" t="n">
-        <v>58584</v>
+        <v>86886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,10 +4969,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R45" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5164,10 +5156,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985902</v>
+        <v>128985896</v>
       </c>
       <c r="B47" t="n">
-        <v>92480</v>
+        <v>92871</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,34 +5167,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720521</v>
+        <v>720577</v>
       </c>
       <c r="R47" t="n">
-        <v>6626387</v>
+        <v>6626370</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5243,6 +5238,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5261,45 +5257,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B48" t="n">
-        <v>86886</v>
+        <v>92871</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R48" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5340,6 +5339,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B24" t="n">
-        <v>92847</v>
+        <v>91048</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R24" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B25" t="n">
-        <v>91048</v>
+        <v>92847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R25" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B43" t="n">
-        <v>92480</v>
+        <v>86886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R43" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4837,45 +4837,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B44" t="n">
-        <v>58584</v>
+        <v>91912</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R44" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4910,6 +4913,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4918,6 +4926,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4934,45 +4962,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B45" t="n">
-        <v>86886</v>
+        <v>92871</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R45" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5013,6 +5044,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5031,32 +5063,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B46" t="n">
-        <v>91912</v>
+        <v>92871</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5069,10 +5101,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R46" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5107,39 +5139,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5156,10 +5164,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B47" t="n">
-        <v>92871</v>
+        <v>92480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,37 +5175,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R47" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5238,7 +5243,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5257,10 +5261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985875</v>
+        <v>128985899</v>
       </c>
       <c r="B48" t="n">
-        <v>92871</v>
+        <v>58584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5268,37 +5272,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720769</v>
+        <v>720542</v>
       </c>
       <c r="R48" t="n">
-        <v>6626395</v>
+        <v>6626391</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5339,7 +5340,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92853</v>
+        <v>92839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>128985905</v>
       </c>
       <c r="B9" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>98700</v>
+        <v>98726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,45 +1965,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92824</v>
+        <v>92857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R15" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2062,48 +2066,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92871</v>
+        <v>92810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R16" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2144,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985860</v>
+        <v>128985866</v>
       </c>
       <c r="B17" t="n">
-        <v>91754</v>
+        <v>92189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720709</v>
+        <v>720790</v>
       </c>
       <c r="R17" t="n">
-        <v>6626266</v>
+        <v>6626254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B18" t="n">
-        <v>92174</v>
+        <v>91763</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R18" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985861</v>
+        <v>128985887</v>
       </c>
       <c r="B19" t="n">
-        <v>92871</v>
+        <v>105754</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2368,37 +2368,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>224098</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720733</v>
+        <v>720586</v>
       </c>
       <c r="R19" t="n">
-        <v>6626258</v>
+        <v>6626407</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,7 +2436,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2458,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B20" t="n">
-        <v>105728</v>
+        <v>92857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2469,34 +2465,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R20" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2537,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985850</v>
+        <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>92480</v>
+        <v>86896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720528</v>
+        <v>720530</v>
       </c>
       <c r="R21" t="n">
-        <v>6626273</v>
+        <v>6626415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985890</v>
+        <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>86895</v>
+        <v>92494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3611</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720530</v>
+        <v>720528</v>
       </c>
       <c r="R22" t="n">
-        <v>6626415</v>
+        <v>6626273</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>91048</v>
+        <v>92833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R24" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>92847</v>
+        <v>91049</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R25" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B28" t="n">
-        <v>92824</v>
+        <v>91313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R28" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B29" t="n">
-        <v>91314</v>
+        <v>92810</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R29" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985893</v>
+        <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>58586</v>
+        <v>89447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208249</v>
+        <v>37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720574</v>
+        <v>720621</v>
       </c>
       <c r="R31" t="n">
-        <v>6626394</v>
+        <v>6626429</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3618,6 +3618,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3644,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985865</v>
+        <v>128985893</v>
       </c>
       <c r="B32" t="n">
-        <v>92871</v>
+        <v>58586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,37 +3660,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720780</v>
+        <v>720574</v>
       </c>
       <c r="R32" t="n">
-        <v>6626277</v>
+        <v>6626394</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3726,7 +3728,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3745,45 +3746,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B33" t="n">
-        <v>89446</v>
+        <v>92857</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R33" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3818,17 +3822,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985876</v>
+        <v>128985852</v>
       </c>
       <c r="B34" t="n">
-        <v>92480</v>
+        <v>92857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,34 +3858,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720766</v>
+        <v>720548</v>
       </c>
       <c r="R34" t="n">
-        <v>6626378</v>
+        <v>6626285</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3926,6 +3929,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3944,10 +3948,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985859</v>
+        <v>128985889</v>
       </c>
       <c r="B35" t="n">
-        <v>92480</v>
+        <v>92857</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,34 +3959,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720718</v>
+        <v>720564</v>
       </c>
       <c r="R35" t="n">
-        <v>6626247</v>
+        <v>6626459</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4023,6 +4030,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4041,10 +4049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985908</v>
+        <v>128985879</v>
       </c>
       <c r="B36" t="n">
-        <v>86970</v>
+        <v>92857</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4052,34 +4060,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720504</v>
+        <v>720754</v>
       </c>
       <c r="R36" t="n">
-        <v>6626377</v>
+        <v>6626384</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4120,6 +4131,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4138,10 +4150,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985852</v>
+        <v>128985876</v>
       </c>
       <c r="B37" t="n">
-        <v>92871</v>
+        <v>92494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4149,37 +4161,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720548</v>
+        <v>720766</v>
       </c>
       <c r="R37" t="n">
-        <v>6626285</v>
+        <v>6626378</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4220,7 +4229,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4239,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985889</v>
+        <v>128985859</v>
       </c>
       <c r="B38" t="n">
-        <v>92871</v>
+        <v>92494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4250,37 +4258,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720564</v>
+        <v>720718</v>
       </c>
       <c r="R38" t="n">
-        <v>6626459</v>
+        <v>6626247</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4321,7 +4326,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B39" t="n">
-        <v>92871</v>
+        <v>86971</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4351,37 +4355,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R39" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4422,7 +4423,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92824</v>
+        <v>92810</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985873</v>
+        <v>128985902</v>
       </c>
       <c r="B43" t="n">
-        <v>86886</v>
+        <v>92494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>445</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720771</v>
+        <v>720521</v>
       </c>
       <c r="R43" t="n">
-        <v>6626378</v>
+        <v>6626387</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4840,7 +4840,7 @@
         <v>128985882</v>
       </c>
       <c r="B44" t="n">
-        <v>91912</v>
+        <v>91921</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4962,48 +4962,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985896</v>
+        <v>128985873</v>
       </c>
       <c r="B45" t="n">
-        <v>92871</v>
+        <v>86887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720577</v>
+        <v>720771</v>
       </c>
       <c r="R45" t="n">
-        <v>6626370</v>
+        <v>6626378</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5044,7 +5041,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5063,10 +5059,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B46" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5101,10 +5097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R46" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5164,10 +5160,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B47" t="n">
-        <v>92480</v>
+        <v>92857</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,34 +5171,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R47" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5243,6 +5242,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,45 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92839</v>
+        <v>92858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R6" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1151,6 +1154,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,48 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R7" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1251,7 +1252,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B8" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R8" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B9" t="n">
-        <v>92857</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,37 +1382,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R9" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,7 +1450,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B10" t="n">
-        <v>98726</v>
+        <v>92858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,34 +1479,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R10" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1551,6 +1550,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92810</v>
+        <v>92811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128985866</v>
       </c>
       <c r="B17" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>128985860</v>
       </c>
       <c r="B18" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B19" t="n">
-        <v>105754</v>
+        <v>92858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2368,34 +2368,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R19" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2436,6 +2439,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2454,10 +2458,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985861</v>
+        <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>92857</v>
+        <v>105756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2469,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>224098</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720733</v>
+        <v>720586</v>
       </c>
       <c r="R20" t="n">
-        <v>6626258</v>
+        <v>6626407</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2537,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B24" t="n">
-        <v>92833</v>
+        <v>91049</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R24" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B25" t="n">
-        <v>91049</v>
+        <v>92834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R25" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>91313</v>
+        <v>92811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R28" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>92810</v>
+        <v>91313</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R29" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985893</v>
+        <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>58586</v>
+        <v>92858</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,34 +3660,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208249</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720574</v>
+        <v>720780</v>
       </c>
       <c r="R32" t="n">
-        <v>6626394</v>
+        <v>6626277</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3728,6 +3731,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3746,10 +3750,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985865</v>
+        <v>128985893</v>
       </c>
       <c r="B33" t="n">
-        <v>92857</v>
+        <v>58586</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3757,37 +3761,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720780</v>
+        <v>720574</v>
       </c>
       <c r="R33" t="n">
-        <v>6626277</v>
+        <v>6626394</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3828,7 +3829,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>128985852</v>
       </c>
       <c r="B34" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>128985889</v>
       </c>
       <c r="B35" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>128985879</v>
       </c>
       <c r="B36" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B37" t="n">
-        <v>92494</v>
+        <v>86971</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R37" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985859</v>
+        <v>128985876</v>
       </c>
       <c r="B38" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720718</v>
+        <v>720766</v>
       </c>
       <c r="R38" t="n">
-        <v>6626247</v>
+        <v>6626378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985908</v>
+        <v>128985859</v>
       </c>
       <c r="B39" t="n">
-        <v>86971</v>
+        <v>92495</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4355,21 +4355,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720504</v>
+        <v>720718</v>
       </c>
       <c r="R39" t="n">
-        <v>6626377</v>
+        <v>6626247</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4444,7 +4444,7 @@
         <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92810</v>
+        <v>92811</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B43" t="n">
-        <v>92494</v>
+        <v>86887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R43" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4837,48 +4837,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B44" t="n">
-        <v>91921</v>
+        <v>92495</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R44" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,11 +4910,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4926,26 +4918,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4962,45 +4934,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B45" t="n">
-        <v>86887</v>
+        <v>92858</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R45" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5041,6 +5016,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5059,10 +5035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985896</v>
+        <v>128985875</v>
       </c>
       <c r="B46" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5097,10 +5073,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720577</v>
+        <v>720769</v>
       </c>
       <c r="R46" t="n">
-        <v>6626370</v>
+        <v>6626395</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5160,32 +5136,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B47" t="n">
-        <v>92857</v>
+        <v>91922</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5198,10 +5174,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R47" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5236,15 +5212,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1270,7 +1270,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985905</v>
+        <v>128985897</v>
       </c>
       <c r="B8" t="n">
         <v>92858</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720491</v>
+        <v>720543</v>
       </c>
       <c r="R8" t="n">
-        <v>6626322</v>
+        <v>6626360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985884</v>
+        <v>128985905</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>92858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,34 +1382,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720568</v>
+        <v>720491</v>
       </c>
       <c r="R9" t="n">
-        <v>6626387</v>
+        <v>6626322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1450,6 +1453,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>92858</v>
+        <v>98728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,37 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R10" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1550,7 +1551,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985900</v>
+        <v>128985854</v>
       </c>
       <c r="B11" t="n">
-        <v>92495</v>
+        <v>92858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,34 +1580,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720544</v>
+        <v>720559</v>
       </c>
       <c r="R11" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1648,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B12" t="n">
-        <v>92495</v>
+        <v>92858</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1677,34 +1681,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R12" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1745,6 +1752,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1763,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B13" t="n">
-        <v>92858</v>
+        <v>92495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1774,37 +1782,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R13" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1845,7 +1850,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B14" t="n">
-        <v>92858</v>
+        <v>92495</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,37 +1879,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R14" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1946,7 +1947,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,48 +1965,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92858</v>
+        <v>92811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2044,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92811</v>
+        <v>92858</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B17" t="n">
-        <v>92190</v>
+        <v>91764</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R17" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,45 +2260,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985860</v>
+        <v>128985861</v>
       </c>
       <c r="B18" t="n">
-        <v>91764</v>
+        <v>92858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720709</v>
+        <v>720733</v>
       </c>
       <c r="R18" t="n">
-        <v>6626266</v>
+        <v>6626258</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2339,6 +2342,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2357,10 +2361,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985861</v>
+        <v>128985866</v>
       </c>
       <c r="B19" t="n">
-        <v>92858</v>
+        <v>92190</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2368,37 +2372,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720733</v>
+        <v>720790</v>
       </c>
       <c r="R19" t="n">
-        <v>6626258</v>
+        <v>6626254</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,7 +2440,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>105756</v>
+        <v>105757</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985890</v>
+        <v>128985850</v>
       </c>
       <c r="B21" t="n">
-        <v>86896</v>
+        <v>92495</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3611</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720530</v>
+        <v>720528</v>
       </c>
       <c r="R21" t="n">
-        <v>6626415</v>
+        <v>6626273</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985850</v>
+        <v>128985890</v>
       </c>
       <c r="B22" t="n">
-        <v>92495</v>
+        <v>86896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720528</v>
+        <v>720530</v>
       </c>
       <c r="R22" t="n">
-        <v>6626273</v>
+        <v>6626415</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985883</v>
+        <v>128985893</v>
       </c>
       <c r="B31" t="n">
-        <v>89447</v>
+        <v>58586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>208249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720621</v>
+        <v>720574</v>
       </c>
       <c r="R31" t="n">
-        <v>6626429</v>
+        <v>6626394</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3618,11 +3618,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3649,48 +3644,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985865</v>
+        <v>128985883</v>
       </c>
       <c r="B32" t="n">
-        <v>92858</v>
+        <v>89447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>37</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720780</v>
+        <v>720621</v>
       </c>
       <c r="R32" t="n">
-        <v>6626277</v>
+        <v>6626429</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3725,13 +3717,17 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3750,10 +3746,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985893</v>
+        <v>128985865</v>
       </c>
       <c r="B33" t="n">
-        <v>58586</v>
+        <v>92858</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3761,34 +3757,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208249</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720574</v>
+        <v>720780</v>
       </c>
       <c r="R33" t="n">
-        <v>6626394</v>
+        <v>6626277</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3829,6 +3828,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4740,45 +4740,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B43" t="n">
-        <v>86887</v>
+        <v>92858</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R43" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4819,6 +4822,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4837,10 +4841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B44" t="n">
-        <v>92495</v>
+        <v>92858</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4848,34 +4852,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R44" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4916,6 +4923,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4934,10 +4942,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B45" t="n">
-        <v>92858</v>
+        <v>92495</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4945,37 +4953,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R45" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5016,7 +5021,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5035,10 +5039,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985875</v>
+        <v>128985899</v>
       </c>
       <c r="B46" t="n">
-        <v>92858</v>
+        <v>58584</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,37 +5050,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720769</v>
+        <v>720542</v>
       </c>
       <c r="R46" t="n">
-        <v>6626395</v>
+        <v>6626391</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5117,7 +5118,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985882</v>
+        <v>128985873</v>
       </c>
       <c r="B47" t="n">
-        <v>91922</v>
+        <v>86887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5147,37 +5147,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1506</v>
+        <v>445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720643</v>
+        <v>720771</v>
       </c>
       <c r="R47" t="n">
-        <v>6626413</v>
+        <v>6626378</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5212,11 +5209,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5225,26 +5217,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5261,45 +5233,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B48" t="n">
-        <v>58584</v>
+        <v>91922</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R48" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5334,6 +5309,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5342,6 +5322,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B8" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R8" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B9" t="n">
-        <v>92858</v>
+        <v>98732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,37 +1382,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R9" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,7 +1450,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B10" t="n">
-        <v>98728</v>
+        <v>92861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,34 +1479,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R10" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1551,6 +1550,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92858</v>
+        <v>92498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,37 +1580,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R11" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1651,7 +1648,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1666,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92858</v>
+        <v>92498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,37 +1677,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R12" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1752,7 +1745,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1771,10 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985900</v>
+        <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,34 +1774,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720544</v>
+        <v>720559</v>
       </c>
       <c r="R13" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1850,6 +1845,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1868,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,34 +1875,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R14" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1947,6 +1946,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92811</v>
+        <v>92814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,32 +2163,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985860</v>
+        <v>128985887</v>
       </c>
       <c r="B17" t="n">
-        <v>91764</v>
+        <v>105761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1106</v>
+        <v>224098</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720709</v>
+        <v>720586</v>
       </c>
       <c r="R17" t="n">
-        <v>6626266</v>
+        <v>6626407</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985861</v>
+        <v>128985866</v>
       </c>
       <c r="B18" t="n">
-        <v>92858</v>
+        <v>92193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,37 +2271,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720733</v>
+        <v>720790</v>
       </c>
       <c r="R18" t="n">
-        <v>6626258</v>
+        <v>6626254</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2342,7 +2339,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2361,32 +2357,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985866</v>
+        <v>128985860</v>
       </c>
       <c r="B19" t="n">
-        <v>92190</v>
+        <v>91767</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2396,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720790</v>
+        <v>720709</v>
       </c>
       <c r="R19" t="n">
-        <v>6626254</v>
+        <v>6626266</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2458,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B20" t="n">
-        <v>105757</v>
+        <v>92861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2469,34 +2465,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R20" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2537,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>128985850</v>
       </c>
       <c r="B21" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985890</v>
       </c>
       <c r="B22" t="n">
-        <v>86896</v>
+        <v>86899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985862</v>
+        <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>91049</v>
+        <v>92837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5741</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720770</v>
+        <v>720496</v>
       </c>
       <c r="R24" t="n">
-        <v>6626291</v>
+        <v>6626331</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985904</v>
+        <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>91052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720496</v>
+        <v>720770</v>
       </c>
       <c r="R25" t="n">
-        <v>6626331</v>
+        <v>6626291</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>128985891</v>
       </c>
       <c r="B27" t="n">
-        <v>79421</v>
+        <v>79423</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B28" t="n">
-        <v>92811</v>
+        <v>91316</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R28" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B29" t="n">
-        <v>91313</v>
+        <v>92814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R29" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985893</v>
+        <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>58586</v>
+        <v>89450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208249</v>
+        <v>37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720574</v>
+        <v>720621</v>
       </c>
       <c r="R31" t="n">
-        <v>6626394</v>
+        <v>6626429</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3618,6 +3618,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3644,45 +3649,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>89447</v>
+        <v>92861</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R32" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3717,17 +3725,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3746,10 +3750,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985865</v>
+        <v>128985893</v>
       </c>
       <c r="B33" t="n">
-        <v>92858</v>
+        <v>58586</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3757,37 +3761,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720780</v>
+        <v>720574</v>
       </c>
       <c r="R33" t="n">
-        <v>6626277</v>
+        <v>6626394</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3828,7 +3829,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985852</v>
+        <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>92858</v>
+        <v>86974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,37 +3858,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720548</v>
+        <v>720504</v>
       </c>
       <c r="R34" t="n">
-        <v>6626285</v>
+        <v>6626377</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3929,7 +3926,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3948,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985889</v>
+        <v>128985876</v>
       </c>
       <c r="B35" t="n">
-        <v>92858</v>
+        <v>92498</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3959,37 +3955,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720564</v>
+        <v>720766</v>
       </c>
       <c r="R35" t="n">
-        <v>6626459</v>
+        <v>6626378</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4030,7 +4023,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4049,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985879</v>
+        <v>128985859</v>
       </c>
       <c r="B36" t="n">
-        <v>92858</v>
+        <v>92498</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4060,37 +4052,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720754</v>
+        <v>720718</v>
       </c>
       <c r="R36" t="n">
-        <v>6626384</v>
+        <v>6626247</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4131,7 +4120,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4150,10 +4138,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985908</v>
+        <v>128985852</v>
       </c>
       <c r="B37" t="n">
-        <v>86971</v>
+        <v>92861</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4161,34 +4149,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720504</v>
+        <v>720548</v>
       </c>
       <c r="R37" t="n">
-        <v>6626377</v>
+        <v>6626285</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,6 +4220,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4247,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985876</v>
+        <v>128985889</v>
       </c>
       <c r="B38" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4258,34 +4250,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720766</v>
+        <v>720564</v>
       </c>
       <c r="R38" t="n">
-        <v>6626378</v>
+        <v>6626459</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4326,6 +4321,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4344,10 +4340,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985859</v>
+        <v>128985879</v>
       </c>
       <c r="B39" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4355,34 +4351,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720718</v>
+        <v>720754</v>
       </c>
       <c r="R39" t="n">
-        <v>6626247</v>
+        <v>6626384</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4423,6 +4422,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92811</v>
+        <v>92814</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B43" t="n">
-        <v>92858</v>
+        <v>92498</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4751,37 +4751,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R43" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4822,7 +4819,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4841,10 +4837,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B44" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R44" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4942,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B45" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4953,34 +4949,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R45" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5021,6 +5020,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5039,45 +5039,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B46" t="n">
-        <v>58584</v>
+        <v>91925</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R46" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5112,6 +5115,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5120,6 +5128,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5139,7 +5167,7 @@
         <v>128985873</v>
       </c>
       <c r="B47" t="n">
-        <v>86887</v>
+        <v>86890</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5233,48 +5261,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985882</v>
+        <v>128985899</v>
       </c>
       <c r="B48" t="n">
-        <v>91922</v>
+        <v>58584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1506</v>
+        <v>208250</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720643</v>
+        <v>720542</v>
       </c>
       <c r="R48" t="n">
-        <v>6626413</v>
+        <v>6626391</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5309,11 +5334,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5322,26 +5342,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985850</v>
+        <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>92498</v>
+        <v>86899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720528</v>
+        <v>720530</v>
       </c>
       <c r="R21" t="n">
-        <v>6626273</v>
+        <v>6626415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985890</v>
+        <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>86899</v>
+        <v>92498</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3611</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720530</v>
+        <v>720528</v>
       </c>
       <c r="R22" t="n">
-        <v>6626415</v>
+        <v>6626273</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>91316</v>
+        <v>92814</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R28" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>92814</v>
+        <v>91316</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R29" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,48 +1072,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92861</v>
+        <v>92845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R6" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1154,7 +1151,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,45 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92843</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R7" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1252,6 +1251,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B8" t="n">
-        <v>92861</v>
+        <v>98734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,37 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R8" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1352,7 +1349,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B9" t="n">
-        <v>98732</v>
+        <v>92863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,34 +1378,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R9" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1450,6 +1449,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B10" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R10" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985900</v>
+        <v>128985854</v>
       </c>
       <c r="B11" t="n">
-        <v>92498</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,34 +1580,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720544</v>
+        <v>720559</v>
       </c>
       <c r="R11" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1648,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1666,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B12" t="n">
-        <v>92498</v>
+        <v>92863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1677,34 +1681,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R12" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1745,6 +1752,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1763,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B13" t="n">
-        <v>92861</v>
+        <v>92500</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1774,37 +1782,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R13" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1845,7 +1850,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B14" t="n">
-        <v>92861</v>
+        <v>92500</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,37 +1879,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R14" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1946,7 +1947,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92814</v>
+        <v>92816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B17" t="n">
-        <v>105761</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,34 +2174,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R17" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,6 +2245,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2263,7 +2267,7 @@
         <v>128985866</v>
       </c>
       <c r="B18" t="n">
-        <v>92193</v>
+        <v>92195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,7 +2364,7 @@
         <v>128985860</v>
       </c>
       <c r="B19" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,10 +2458,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985861</v>
+        <v>128985887</v>
       </c>
       <c r="B20" t="n">
-        <v>92861</v>
+        <v>105763</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2469,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>224098</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720733</v>
+        <v>720586</v>
       </c>
       <c r="R20" t="n">
-        <v>6626258</v>
+        <v>6626407</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2537,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>86899</v>
+        <v>86901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>91052</v>
+        <v>91054</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>128985891</v>
       </c>
       <c r="B27" t="n">
-        <v>79423</v>
+        <v>79424</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>92814</v>
+        <v>92816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>89450</v>
+        <v>89452</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>86974</v>
+        <v>86976</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985876</v>
+        <v>128985852</v>
       </c>
       <c r="B35" t="n">
-        <v>92498</v>
+        <v>92863</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,34 +3955,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720766</v>
+        <v>720548</v>
       </c>
       <c r="R35" t="n">
-        <v>6626378</v>
+        <v>6626285</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4023,6 +4026,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4041,10 +4045,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985859</v>
+        <v>128985889</v>
       </c>
       <c r="B36" t="n">
-        <v>92498</v>
+        <v>92863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4052,34 +4056,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720718</v>
+        <v>720564</v>
       </c>
       <c r="R36" t="n">
-        <v>6626247</v>
+        <v>6626459</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4120,6 +4127,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4138,10 +4146,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985852</v>
+        <v>128985879</v>
       </c>
       <c r="B37" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720548</v>
+        <v>720754</v>
       </c>
       <c r="R37" t="n">
-        <v>6626285</v>
+        <v>6626384</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4239,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985889</v>
+        <v>128985876</v>
       </c>
       <c r="B38" t="n">
-        <v>92861</v>
+        <v>92500</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4250,37 +4258,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720564</v>
+        <v>720766</v>
       </c>
       <c r="R38" t="n">
-        <v>6626459</v>
+        <v>6626378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4321,7 +4326,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985879</v>
+        <v>128985859</v>
       </c>
       <c r="B39" t="n">
-        <v>92861</v>
+        <v>92500</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4351,37 +4355,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720754</v>
+        <v>720718</v>
       </c>
       <c r="R39" t="n">
-        <v>6626384</v>
+        <v>6626247</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4422,7 +4423,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92814</v>
+        <v>92816</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B43" t="n">
-        <v>92498</v>
+        <v>86892</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R43" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4837,32 +4837,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985896</v>
+        <v>128985882</v>
       </c>
       <c r="B44" t="n">
-        <v>92861</v>
+        <v>91927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720577</v>
+        <v>720643</v>
       </c>
       <c r="R44" t="n">
-        <v>6626370</v>
+        <v>6626413</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,15 +4913,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4938,10 +4962,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B45" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4976,10 +5000,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R45" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5039,32 +5063,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B46" t="n">
-        <v>91925</v>
+        <v>92863</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5077,10 +5101,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R46" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5115,39 +5139,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985873</v>
+        <v>128985902</v>
       </c>
       <c r="B47" t="n">
-        <v>86890</v>
+        <v>92500</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>445</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720771</v>
+        <v>720521</v>
       </c>
       <c r="R47" t="n">
-        <v>6626378</v>
+        <v>6626387</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92845</v>
+        <v>92849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>98734</v>
+        <v>92867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R8" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1349,6 +1352,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R9" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>98738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,37 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R10" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1550,7 +1551,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>128985854</v>
       </c>
       <c r="B11" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128985888</v>
       </c>
       <c r="B12" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B13" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R13" t="n">
         <v>6626397</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B14" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R14" t="n">
         <v>6626397</v>
@@ -1965,45 +1965,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92816</v>
+        <v>92867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R15" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2062,48 +2066,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>92820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R16" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2144,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,48 +2163,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985861</v>
+        <v>128985860</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>91773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>1106</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720733</v>
+        <v>720709</v>
       </c>
       <c r="R17" t="n">
-        <v>6626258</v>
+        <v>6626266</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2245,7 +2242,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2264,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985866</v>
+        <v>128985887</v>
       </c>
       <c r="B18" t="n">
-        <v>92195</v>
+        <v>105767</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2275,21 +2271,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>224098</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2299,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720790</v>
+        <v>720586</v>
       </c>
       <c r="R18" t="n">
-        <v>6626254</v>
+        <v>6626407</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2361,32 +2357,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985860</v>
+        <v>128985866</v>
       </c>
       <c r="B19" t="n">
-        <v>91769</v>
+        <v>92199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2396,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720709</v>
+        <v>720790</v>
       </c>
       <c r="R19" t="n">
-        <v>6626266</v>
+        <v>6626254</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2458,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985887</v>
+        <v>128985861</v>
       </c>
       <c r="B20" t="n">
-        <v>105763</v>
+        <v>92867</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2469,34 +2465,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224098</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720586</v>
+        <v>720733</v>
       </c>
       <c r="R20" t="n">
-        <v>6626407</v>
+        <v>6626258</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2537,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>86901</v>
+        <v>86905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>91054</v>
+        <v>91058</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B28" t="n">
-        <v>92816</v>
+        <v>91322</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R28" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B29" t="n">
-        <v>91318</v>
+        <v>92820</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R29" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>89452</v>
+        <v>89456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>128985852</v>
       </c>
       <c r="B35" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>128985889</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128985879</v>
       </c>
       <c r="B37" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>128985876</v>
       </c>
       <c r="B38" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>128985859</v>
       </c>
       <c r="B39" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4441,45 +4441,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128985906</v>
+        <v>128985895</v>
       </c>
       <c r="B40" t="n">
-        <v>92816</v>
+        <v>92867</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720486</v>
+        <v>720572</v>
       </c>
       <c r="R40" t="n">
-        <v>6626330</v>
+        <v>6626395</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4520,6 +4523,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4538,48 +4542,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128985885</v>
+        <v>128985906</v>
       </c>
       <c r="B41" t="n">
-        <v>92863</v>
+        <v>92820</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720573</v>
+        <v>720486</v>
       </c>
       <c r="R41" t="n">
-        <v>6626380</v>
+        <v>6626330</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4620,7 +4621,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4639,10 +4639,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128985895</v>
+        <v>128985885</v>
       </c>
       <c r="B42" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720572</v>
+        <v>720573</v>
       </c>
       <c r="R42" t="n">
-        <v>6626395</v>
+        <v>6626380</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4740,45 +4740,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B43" t="n">
-        <v>86892</v>
+        <v>92867</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R43" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4819,6 +4822,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4837,32 +4841,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B44" t="n">
-        <v>91927</v>
+        <v>92867</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R44" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,39 +4917,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4962,10 +4942,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985896</v>
+        <v>128985899</v>
       </c>
       <c r="B45" t="n">
-        <v>92863</v>
+        <v>58584</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4973,37 +4953,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720577</v>
+        <v>720542</v>
       </c>
       <c r="R45" t="n">
-        <v>6626370</v>
+        <v>6626391</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5044,7 +5021,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5063,32 +5039,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B46" t="n">
-        <v>92863</v>
+        <v>91931</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5101,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R46" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5139,15 +5115,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B47" t="n">
-        <v>92500</v>
+        <v>86896</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R47" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985899</v>
+        <v>128985902</v>
       </c>
       <c r="B48" t="n">
-        <v>58584</v>
+        <v>92504</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,21 +5272,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208250</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720542</v>
+        <v>720521</v>
       </c>
       <c r="R48" t="n">
-        <v>6626391</v>
+        <v>6626387</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128985878</v>
       </c>
       <c r="B6" t="n">
-        <v>92849</v>
+        <v>92850</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128985894</v>
       </c>
       <c r="B7" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B8" t="n">
-        <v>92867</v>
+        <v>98746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,37 +1281,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R8" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1352,7 +1349,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985905</v>
+        <v>128985897</v>
       </c>
       <c r="B9" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720491</v>
+        <v>720543</v>
       </c>
       <c r="R9" t="n">
-        <v>6626322</v>
+        <v>6626360</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985884</v>
+        <v>128985905</v>
       </c>
       <c r="B10" t="n">
-        <v>98738</v>
+        <v>92868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,34 +1479,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720568</v>
+        <v>720491</v>
       </c>
       <c r="R10" t="n">
-        <v>6626387</v>
+        <v>6626322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1551,6 +1550,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985854</v>
+        <v>128985900</v>
       </c>
       <c r="B11" t="n">
-        <v>92867</v>
+        <v>92505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,37 +1580,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720559</v>
+        <v>720544</v>
       </c>
       <c r="R11" t="n">
-        <v>6626267</v>
+        <v>6626397</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1651,7 +1648,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1670,10 +1666,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B12" t="n">
-        <v>92867</v>
+        <v>92505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,37 +1677,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R12" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1752,7 +1745,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1771,10 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985886</v>
+        <v>128985854</v>
       </c>
       <c r="B13" t="n">
-        <v>92504</v>
+        <v>92868</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,34 +1774,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720581</v>
+        <v>720559</v>
       </c>
       <c r="R13" t="n">
-        <v>6626397</v>
+        <v>6626267</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1850,6 +1845,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1868,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985900</v>
+        <v>128985888</v>
       </c>
       <c r="B14" t="n">
-        <v>92504</v>
+        <v>92868</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,34 +1875,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720544</v>
+        <v>720578</v>
       </c>
       <c r="R14" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1947,6 +1946,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1965,48 +1965,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B15" t="n">
-        <v>92867</v>
+        <v>92821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2044,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,45 +2062,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B16" t="n">
-        <v>92820</v>
+        <v>92868</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,6 +2144,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,45 +2163,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985860</v>
+        <v>128985861</v>
       </c>
       <c r="B17" t="n">
-        <v>91773</v>
+        <v>92868</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1106</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720709</v>
+        <v>720733</v>
       </c>
       <c r="R17" t="n">
-        <v>6626266</v>
+        <v>6626258</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,6 +2245,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2263,7 +2267,7 @@
         <v>128985887</v>
       </c>
       <c r="B18" t="n">
-        <v>105767</v>
+        <v>105777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,7 +2364,7 @@
         <v>128985866</v>
       </c>
       <c r="B19" t="n">
-        <v>92199</v>
+        <v>92200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,48 +2458,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985861</v>
+        <v>128985860</v>
       </c>
       <c r="B20" t="n">
-        <v>92867</v>
+        <v>91774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>1106</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720733</v>
+        <v>720709</v>
       </c>
       <c r="R20" t="n">
-        <v>6626258</v>
+        <v>6626266</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2537,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>128985890</v>
       </c>
       <c r="B21" t="n">
-        <v>86905</v>
+        <v>86906</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>128985850</v>
       </c>
       <c r="B22" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>128985839</v>
       </c>
       <c r="B23" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>128985904</v>
       </c>
       <c r="B24" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128985862</v>
       </c>
       <c r="B25" t="n">
-        <v>91058</v>
+        <v>91059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>128985901</v>
       </c>
       <c r="B26" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,32 +3256,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985898</v>
+        <v>128985853</v>
       </c>
       <c r="B28" t="n">
-        <v>91322</v>
+        <v>92821</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720530</v>
+        <v>720573</v>
       </c>
       <c r="R28" t="n">
-        <v>6626369</v>
+        <v>6626278</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3353,32 +3353,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985853</v>
+        <v>128985898</v>
       </c>
       <c r="B29" t="n">
-        <v>92820</v>
+        <v>91323</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R29" t="n">
-        <v>6626278</v>
+        <v>6626369</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3453,7 +3453,7 @@
         <v>128985907</v>
       </c>
       <c r="B30" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,45 +3547,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B31" t="n">
-        <v>89456</v>
+        <v>92868</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R31" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3620,17 +3623,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3649,48 +3648,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985865</v>
+        <v>128985883</v>
       </c>
       <c r="B32" t="n">
-        <v>92867</v>
+        <v>89457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>37</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720780</v>
+        <v>720621</v>
       </c>
       <c r="R32" t="n">
-        <v>6626277</v>
+        <v>6626429</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3725,13 +3721,17 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B34" t="n">
-        <v>86980</v>
+        <v>92505</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R34" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985852</v>
+        <v>128985859</v>
       </c>
       <c r="B35" t="n">
-        <v>92867</v>
+        <v>92505</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,37 +3955,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720548</v>
+        <v>720718</v>
       </c>
       <c r="R35" t="n">
-        <v>6626285</v>
+        <v>6626247</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4026,7 +4023,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4045,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985889</v>
+        <v>128985908</v>
       </c>
       <c r="B36" t="n">
-        <v>92867</v>
+        <v>86981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4056,37 +4052,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720564</v>
+        <v>720504</v>
       </c>
       <c r="R36" t="n">
-        <v>6626459</v>
+        <v>6626377</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4127,7 +4120,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4138,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985879</v>
+        <v>128985852</v>
       </c>
       <c r="B37" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4184,10 +4176,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720754</v>
+        <v>720548</v>
       </c>
       <c r="R37" t="n">
-        <v>6626384</v>
+        <v>6626285</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4247,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985876</v>
+        <v>128985889</v>
       </c>
       <c r="B38" t="n">
-        <v>92504</v>
+        <v>92868</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4258,34 +4250,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720766</v>
+        <v>720564</v>
       </c>
       <c r="R38" t="n">
-        <v>6626378</v>
+        <v>6626459</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4326,6 +4321,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4344,10 +4340,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985859</v>
+        <v>128985879</v>
       </c>
       <c r="B39" t="n">
-        <v>92504</v>
+        <v>92868</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4355,34 +4351,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720718</v>
+        <v>720754</v>
       </c>
       <c r="R39" t="n">
-        <v>6626247</v>
+        <v>6626384</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4423,6 +4422,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4441,48 +4441,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128985895</v>
+        <v>128985906</v>
       </c>
       <c r="B40" t="n">
-        <v>92867</v>
+        <v>92821</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720572</v>
+        <v>720486</v>
       </c>
       <c r="R40" t="n">
-        <v>6626395</v>
+        <v>6626330</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4523,7 +4520,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4542,45 +4538,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128985906</v>
+        <v>128985885</v>
       </c>
       <c r="B41" t="n">
-        <v>92820</v>
+        <v>92868</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720486</v>
+        <v>720573</v>
       </c>
       <c r="R41" t="n">
-        <v>6626330</v>
+        <v>6626380</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4621,6 +4620,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4639,10 +4639,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128985885</v>
+        <v>128985895</v>
       </c>
       <c r="B42" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720573</v>
+        <v>720572</v>
       </c>
       <c r="R42" t="n">
-        <v>6626380</v>
+        <v>6626395</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4740,48 +4740,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985896</v>
+        <v>128985873</v>
       </c>
       <c r="B43" t="n">
-        <v>92867</v>
+        <v>86897</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720577</v>
+        <v>720771</v>
       </c>
       <c r="R43" t="n">
-        <v>6626370</v>
+        <v>6626378</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4822,7 +4819,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4841,10 +4837,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B44" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R44" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4942,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985899</v>
+        <v>128985875</v>
       </c>
       <c r="B45" t="n">
-        <v>58584</v>
+        <v>92868</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4953,34 +4949,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208250</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720542</v>
+        <v>720769</v>
       </c>
       <c r="R45" t="n">
-        <v>6626391</v>
+        <v>6626395</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5021,6 +5020,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5039,48 +5039,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985882</v>
+        <v>128985899</v>
       </c>
       <c r="B46" t="n">
-        <v>91931</v>
+        <v>58584</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>208250</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720643</v>
+        <v>720542</v>
       </c>
       <c r="R46" t="n">
-        <v>6626413</v>
+        <v>6626391</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5115,11 +5112,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5128,26 +5120,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5164,10 +5136,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B47" t="n">
-        <v>86896</v>
+        <v>91932</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,34 +5147,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R47" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5237,6 +5212,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5245,6 +5225,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5264,7 +5264,7 @@
         <v>128985902</v>
       </c>
       <c r="B48" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -1072,45 +1072,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B6" t="n">
-        <v>92850</v>
+        <v>92868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R6" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1151,6 +1154,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,48 +1173,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B7" t="n">
-        <v>92868</v>
+        <v>92850</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R7" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1251,7 +1252,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B8" t="n">
-        <v>98746</v>
+        <v>92868</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,34 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R8" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1349,6 +1352,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1367,7 +1371,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985897</v>
+        <v>128985905</v>
       </c>
       <c r="B9" t="n">
         <v>92868</v>
@@ -1405,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720543</v>
+        <v>720491</v>
       </c>
       <c r="R9" t="n">
-        <v>6626360</v>
+        <v>6626322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985905</v>
+        <v>128985884</v>
       </c>
       <c r="B10" t="n">
-        <v>92868</v>
+        <v>98746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,37 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720491</v>
+        <v>720568</v>
       </c>
       <c r="R10" t="n">
-        <v>6626322</v>
+        <v>6626387</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1550,7 +1551,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1965,45 +1965,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985903</v>
+        <v>128985863</v>
       </c>
       <c r="B15" t="n">
-        <v>92821</v>
+        <v>92868</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720482</v>
+        <v>720755</v>
       </c>
       <c r="R15" t="n">
-        <v>6626323</v>
+        <v>6626301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2044,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2062,48 +2066,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985863</v>
+        <v>128985903</v>
       </c>
       <c r="B16" t="n">
-        <v>92868</v>
+        <v>92821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720755</v>
+        <v>720482</v>
       </c>
       <c r="R16" t="n">
-        <v>6626301</v>
+        <v>6626323</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2144,7 +2145,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985861</v>
+        <v>128985866</v>
       </c>
       <c r="B17" t="n">
-        <v>92868</v>
+        <v>92200</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,37 +2174,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720733</v>
+        <v>720790</v>
       </c>
       <c r="R17" t="n">
-        <v>6626258</v>
+        <v>6626254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2245,7 +2242,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2264,32 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985887</v>
+        <v>128985860</v>
       </c>
       <c r="B18" t="n">
-        <v>105777</v>
+        <v>91774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>224098</v>
+        <v>1106</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2299,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720586</v>
+        <v>720709</v>
       </c>
       <c r="R18" t="n">
-        <v>6626407</v>
+        <v>6626266</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2361,10 +2357,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985866</v>
+        <v>128985887</v>
       </c>
       <c r="B19" t="n">
-        <v>92200</v>
+        <v>105777</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2372,21 +2368,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>224098</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2396,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720790</v>
+        <v>720586</v>
       </c>
       <c r="R19" t="n">
-        <v>6626254</v>
+        <v>6626407</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2458,45 +2454,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985860</v>
+        <v>128985861</v>
       </c>
       <c r="B20" t="n">
-        <v>91774</v>
+        <v>92868</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1106</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720709</v>
+        <v>720733</v>
       </c>
       <c r="R20" t="n">
-        <v>6626266</v>
+        <v>6626258</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2537,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3547,48 +3547,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985865</v>
+        <v>128985883</v>
       </c>
       <c r="B31" t="n">
-        <v>92868</v>
+        <v>89457</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720780</v>
+        <v>720621</v>
       </c>
       <c r="R31" t="n">
-        <v>6626277</v>
+        <v>6626429</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3623,13 +3620,17 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3648,45 +3649,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B32" t="n">
-        <v>89457</v>
+        <v>92868</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R32" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3721,17 +3725,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B34" t="n">
-        <v>92505</v>
+        <v>86981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R34" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985859</v>
+        <v>128985852</v>
       </c>
       <c r="B35" t="n">
-        <v>92505</v>
+        <v>92868</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,34 +3955,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720718</v>
+        <v>720548</v>
       </c>
       <c r="R35" t="n">
-        <v>6626247</v>
+        <v>6626285</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4023,6 +4026,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4041,10 +4045,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985908</v>
+        <v>128985889</v>
       </c>
       <c r="B36" t="n">
-        <v>86981</v>
+        <v>92868</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4052,34 +4056,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720504</v>
+        <v>720564</v>
       </c>
       <c r="R36" t="n">
-        <v>6626377</v>
+        <v>6626459</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4120,6 +4127,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4138,7 +4146,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985852</v>
+        <v>128985879</v>
       </c>
       <c r="B37" t="n">
         <v>92868</v>
@@ -4176,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720548</v>
+        <v>720754</v>
       </c>
       <c r="R37" t="n">
-        <v>6626285</v>
+        <v>6626384</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4239,10 +4247,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985889</v>
+        <v>128985876</v>
       </c>
       <c r="B38" t="n">
-        <v>92868</v>
+        <v>92505</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4250,37 +4258,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720564</v>
+        <v>720766</v>
       </c>
       <c r="R38" t="n">
-        <v>6626459</v>
+        <v>6626378</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4321,7 +4326,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985879</v>
+        <v>128985859</v>
       </c>
       <c r="B39" t="n">
-        <v>92868</v>
+        <v>92505</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4351,37 +4355,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720754</v>
+        <v>720718</v>
       </c>
       <c r="R39" t="n">
-        <v>6626384</v>
+        <v>6626247</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4422,7 +4423,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4837,32 +4837,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985896</v>
+        <v>128985882</v>
       </c>
       <c r="B44" t="n">
-        <v>92868</v>
+        <v>91932</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720577</v>
+        <v>720643</v>
       </c>
       <c r="R44" t="n">
-        <v>6626370</v>
+        <v>6626413</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,15 +4913,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4938,7 +4962,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B45" t="n">
         <v>92868</v>
@@ -4976,10 +5000,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R45" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5039,10 +5063,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985899</v>
+        <v>128985875</v>
       </c>
       <c r="B46" t="n">
-        <v>58584</v>
+        <v>92868</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5050,34 +5074,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>208250</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720542</v>
+        <v>720769</v>
       </c>
       <c r="R46" t="n">
-        <v>6626391</v>
+        <v>6626395</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5118,6 +5145,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5136,48 +5164,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B47" t="n">
-        <v>91932</v>
+        <v>92505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R47" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5212,11 +5237,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5225,26 +5245,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5261,10 +5261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985902</v>
+        <v>128985899</v>
       </c>
       <c r="B48" t="n">
-        <v>92505</v>
+        <v>58584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,21 +5272,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>208250</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720521</v>
+        <v>720542</v>
       </c>
       <c r="R48" t="n">
-        <v>6626387</v>
+        <v>6626391</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2555,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985890</v>
+        <v>128985850</v>
       </c>
       <c r="B21" t="n">
-        <v>86906</v>
+        <v>92505</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3611</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720530</v>
+        <v>720528</v>
       </c>
       <c r="R21" t="n">
-        <v>6626415</v>
+        <v>6626273</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2652,32 +2652,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985850</v>
+        <v>128985890</v>
       </c>
       <c r="B22" t="n">
-        <v>92505</v>
+        <v>86906</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720528</v>
+        <v>720530</v>
       </c>
       <c r="R22" t="n">
-        <v>6626273</v>
+        <v>6626415</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3547,45 +3547,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985883</v>
+        <v>128985865</v>
       </c>
       <c r="B31" t="n">
-        <v>89457</v>
+        <v>92868</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720621</v>
+        <v>720780</v>
       </c>
       <c r="R31" t="n">
-        <v>6626429</v>
+        <v>6626277</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3620,17 +3623,13 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3649,10 +3648,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985865</v>
+        <v>128985893</v>
       </c>
       <c r="B32" t="n">
-        <v>92868</v>
+        <v>58586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3660,37 +3659,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720780</v>
+        <v>720574</v>
       </c>
       <c r="R32" t="n">
-        <v>6626277</v>
+        <v>6626394</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3731,7 +3727,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3750,32 +3745,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985893</v>
+        <v>128985883</v>
       </c>
       <c r="B33" t="n">
-        <v>58586</v>
+        <v>89457</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208249</v>
+        <v>37</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720574</v>
+        <v>720621</v>
       </c>
       <c r="R33" t="n">
-        <v>6626394</v>
+        <v>6626429</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3821,6 +3816,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4538,7 +4538,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128985885</v>
+        <v>128985895</v>
       </c>
       <c r="B41" t="n">
         <v>92868</v>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720573</v>
+        <v>720572</v>
       </c>
       <c r="R41" t="n">
-        <v>6626380</v>
+        <v>6626395</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128985895</v>
+        <v>128985885</v>
       </c>
       <c r="B42" t="n">
         <v>92868</v>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720572</v>
+        <v>720573</v>
       </c>
       <c r="R42" t="n">
-        <v>6626395</v>
+        <v>6626380</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4740,45 +4740,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B43" t="n">
-        <v>86897</v>
+        <v>92868</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R43" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4819,6 +4822,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4837,32 +4841,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B44" t="n">
-        <v>91932</v>
+        <v>92868</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R44" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,39 +4917,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4962,48 +4942,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985896</v>
+        <v>128985873</v>
       </c>
       <c r="B45" t="n">
-        <v>92868</v>
+        <v>86897</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720577</v>
+        <v>720771</v>
       </c>
       <c r="R45" t="n">
-        <v>6626370</v>
+        <v>6626378</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5044,7 +5021,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5063,32 +5039,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B46" t="n">
-        <v>92868</v>
+        <v>91932</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5101,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R46" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5139,15 +5115,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5356,6 +5356,208 @@
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131431262</v>
+      </c>
+      <c r="B49" t="n">
+        <v>93104</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bollen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>720598</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6626321</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131431264</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bollen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>720729</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6626290</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>131431262</v>
       </c>
       <c r="B49" t="n">
-        <v>93109</v>
+        <v>93115</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>131431264</v>
       </c>
       <c r="B50" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>131431262</v>
       </c>
       <c r="B49" t="n">
-        <v>93115</v>
+        <v>93116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>131431262</v>
       </c>
       <c r="B49" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>131431264</v>
       </c>
       <c r="B50" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>131431262</v>
       </c>
       <c r="B49" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>131431264</v>
       </c>
       <c r="B50" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>131431262</v>
       </c>
       <c r="B49" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>131431264</v>
       </c>
       <c r="B50" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>131431262</v>
       </c>
       <c r="B49" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>131431264</v>
       </c>
       <c r="B50" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>131431262</v>
       </c>
       <c r="B49" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>131431264</v>
       </c>
       <c r="B50" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124663398</v>
+        <v>128985851</v>
       </c>
       <c r="B2" t="n">
-        <v>91792</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pilkrogsudden, Upl</t>
+          <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720795</v>
+        <v>720526</v>
       </c>
       <c r="R2" t="n">
-        <v>6626271</v>
+        <v>6626269</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,69 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124665953</v>
+        <v>128985853</v>
       </c>
       <c r="B3" t="n">
-        <v>98291</v>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720564</v>
+        <v>720573</v>
       </c>
       <c r="R3" t="n">
-        <v>6626375</v>
+        <v>6626278</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,60 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124664322</v>
+        <v>128985903</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720870</v>
+        <v>720482</v>
       </c>
       <c r="R4" t="n">
-        <v>6626379</v>
+        <v>6626323</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -943,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,60 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124664292</v>
+        <v>128985906</v>
       </c>
       <c r="B5" t="n">
-        <v>91184</v>
+        <v>93186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmängsviken, Upl</t>
+          <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720870</v>
+        <v>720486</v>
       </c>
       <c r="R5" t="n">
-        <v>6626379</v>
+        <v>6626330</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1040,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1060,60 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985894</v>
+        <v>128985860</v>
       </c>
       <c r="B6" t="n">
-        <v>92868</v>
+        <v>92134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>1106</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720563</v>
+        <v>720709</v>
       </c>
       <c r="R6" t="n">
-        <v>6626412</v>
+        <v>6626266</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1154,7 +1142,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1173,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985878</v>
+        <v>124663398</v>
       </c>
       <c r="B7" t="n">
-        <v>92850</v>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720769</v>
+        <v>720795</v>
       </c>
       <c r="R7" t="n">
-        <v>6626378</v>
+        <v>6626271</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1238,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1258,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985897</v>
+        <v>128985866</v>
       </c>
       <c r="B8" t="n">
-        <v>92868</v>
+        <v>92564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,37 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720543</v>
+        <v>720790</v>
       </c>
       <c r="R8" t="n">
-        <v>6626360</v>
+        <v>6626254</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1352,7 +1336,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,51 +1354,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985905</v>
+        <v>124663540</v>
       </c>
       <c r="B9" t="n">
-        <v>92868</v>
+        <v>85532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>1971</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720491</v>
+        <v>720813</v>
       </c>
       <c r="R9" t="n">
-        <v>6626322</v>
+        <v>6626211</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1453,51 +1433,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985884</v>
+        <v>128985849</v>
       </c>
       <c r="B10" t="n">
-        <v>98746</v>
+        <v>87322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>1988</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1507,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720568</v>
+        <v>720518</v>
       </c>
       <c r="R10" t="n">
-        <v>6626387</v>
+        <v>6626271</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1569,48 +1548,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985900</v>
+        <v>131431263</v>
       </c>
       <c r="B11" t="n">
-        <v>92505</v>
+        <v>91361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>3286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720544</v>
+        <v>720499</v>
       </c>
       <c r="R11" t="n">
-        <v>6626397</v>
+        <v>6626262</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1634,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1654,44 +1633,48 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985886</v>
+        <v>128985867</v>
       </c>
       <c r="B12" t="n">
-        <v>92505</v>
+        <v>87375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>3739</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1701,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720581</v>
+        <v>720766</v>
       </c>
       <c r="R12" t="n">
-        <v>6626397</v>
+        <v>6626215</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1763,48 +1746,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985854</v>
+        <v>128985857</v>
       </c>
       <c r="B13" t="n">
-        <v>92868</v>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720559</v>
+        <v>720634</v>
       </c>
       <c r="R13" t="n">
-        <v>6626267</v>
+        <v>6626250</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1845,7 +1825,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1864,51 +1843,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985888</v>
+        <v>131431262</v>
       </c>
       <c r="B14" t="n">
-        <v>92868</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720578</v>
+        <v>720598</v>
       </c>
       <c r="R14" t="n">
-        <v>6626426</v>
+        <v>6626321</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1932,12 +1908,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,67 +1922,67 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985863</v>
+        <v>128985904</v>
       </c>
       <c r="B15" t="n">
-        <v>92868</v>
+        <v>93209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720755</v>
+        <v>720496</v>
       </c>
       <c r="R15" t="n">
-        <v>6626301</v>
+        <v>6626331</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2047,7 +2023,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,32 +2041,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985903</v>
+        <v>128985850</v>
       </c>
       <c r="B16" t="n">
-        <v>92821</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720482</v>
+        <v>720528</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626273</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2163,10 +2138,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985866</v>
+        <v>128985856</v>
       </c>
       <c r="B17" t="n">
-        <v>92200</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,21 +2149,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1339</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720790</v>
+        <v>720577</v>
       </c>
       <c r="R17" t="n">
-        <v>6626254</v>
+        <v>6626263</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2260,32 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985860</v>
+        <v>128985859</v>
       </c>
       <c r="B18" t="n">
-        <v>91774</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720709</v>
+        <v>720718</v>
       </c>
       <c r="R18" t="n">
-        <v>6626266</v>
+        <v>6626247</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2357,32 +2332,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985887</v>
+        <v>128985862</v>
       </c>
       <c r="B19" t="n">
-        <v>105777</v>
+        <v>91409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>224098</v>
+        <v>5741</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2392,10 +2367,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720586</v>
+        <v>720770</v>
       </c>
       <c r="R19" t="n">
-        <v>6626407</v>
+        <v>6626291</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,14 +2429,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985861</v>
+        <v>128985839</v>
       </c>
       <c r="B20" t="n">
-        <v>92868</v>
+        <v>93233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2492,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720733</v>
+        <v>720497</v>
       </c>
       <c r="R20" t="n">
-        <v>6626258</v>
+        <v>6626297</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2555,45 +2530,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985850</v>
+        <v>128985846</v>
       </c>
       <c r="B21" t="n">
-        <v>92505</v>
+        <v>93233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720528</v>
+        <v>720485</v>
       </c>
       <c r="R21" t="n">
-        <v>6626273</v>
+        <v>6626258</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2634,6 +2612,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985890</v>
+        <v>128985847</v>
       </c>
       <c r="B22" t="n">
-        <v>86906</v>
+        <v>93233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,34 +2642,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3611</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720530</v>
+        <v>720493</v>
       </c>
       <c r="R22" t="n">
-        <v>6626415</v>
+        <v>6626265</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2731,6 +2713,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2749,14 +2732,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985839</v>
+        <v>128985852</v>
       </c>
       <c r="B23" t="n">
-        <v>92868</v>
+        <v>93233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2787,10 +2770,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720497</v>
+        <v>720548</v>
       </c>
       <c r="R23" t="n">
-        <v>6626297</v>
+        <v>6626285</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2850,45 +2833,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985904</v>
+        <v>128985854</v>
       </c>
       <c r="B24" t="n">
-        <v>92844</v>
+        <v>93233</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720496</v>
+        <v>720559</v>
       </c>
       <c r="R24" t="n">
-        <v>6626331</v>
+        <v>6626267</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2929,6 +2915,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2947,45 +2934,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985862</v>
+        <v>128985861</v>
       </c>
       <c r="B25" t="n">
-        <v>91059</v>
+        <v>93233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720770</v>
+        <v>720733</v>
       </c>
       <c r="R25" t="n">
-        <v>6626291</v>
+        <v>6626258</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3026,6 +3016,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3044,45 +3035,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128985901</v>
+        <v>128985863</v>
       </c>
       <c r="B26" t="n">
-        <v>92505</v>
+        <v>93233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720521</v>
+        <v>720755</v>
       </c>
       <c r="R26" t="n">
-        <v>6626398</v>
+        <v>6626301</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3123,6 +3117,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3141,32 +3136,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128985891</v>
+        <v>128985865</v>
       </c>
       <c r="B27" t="n">
-        <v>79424</v>
+        <v>93233</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6431</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720531</v>
+        <v>720780</v>
       </c>
       <c r="R27" t="n">
-        <v>6626414</v>
+        <v>6626277</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3223,23 +3218,9 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3256,45 +3237,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128985853</v>
+        <v>128985897</v>
       </c>
       <c r="B28" t="n">
-        <v>92821</v>
+        <v>93233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720573</v>
+        <v>720543</v>
       </c>
       <c r="R28" t="n">
-        <v>6626278</v>
+        <v>6626360</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3335,6 +3319,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3353,45 +3338,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128985898</v>
+        <v>128985905</v>
       </c>
       <c r="B29" t="n">
-        <v>91323</v>
+        <v>93233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720530</v>
+        <v>720491</v>
       </c>
       <c r="R29" t="n">
-        <v>6626369</v>
+        <v>6626322</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3432,6 +3420,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3450,45 +3439,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128985907</v>
+        <v>128985912</v>
       </c>
       <c r="B30" t="n">
-        <v>100913</v>
+        <v>93233</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720516</v>
+        <v>720460</v>
       </c>
       <c r="R30" t="n">
-        <v>6626359</v>
+        <v>6626281</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3529,6 +3521,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3547,10 +3540,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128985865</v>
+        <v>124663137</v>
       </c>
       <c r="B31" t="n">
-        <v>92868</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3558,40 +3551,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720780</v>
+        <v>720673</v>
       </c>
       <c r="R31" t="n">
-        <v>6626277</v>
+        <v>6626244</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3615,12 +3610,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3629,29 +3624,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128985893</v>
+        <v>131431264</v>
       </c>
       <c r="B32" t="n">
-        <v>58586</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3659,37 +3653,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208249</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720574</v>
+        <v>720729</v>
       </c>
       <c r="R32" t="n">
-        <v>6626394</v>
+        <v>6626290</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3713,12 +3707,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3733,60 +3727,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128985883</v>
+        <v>124663221</v>
       </c>
       <c r="B33" t="n">
-        <v>89457</v>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>37</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720621</v>
+        <v>720673</v>
       </c>
       <c r="R33" t="n">
-        <v>6626429</v>
+        <v>6626244</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3810,17 +3808,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Under björk, gran och hassel i vildsvinsbök.</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3835,22 +3828,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128985908</v>
+        <v>128985858</v>
       </c>
       <c r="B34" t="n">
-        <v>86981</v>
+        <v>101325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3858,21 +3851,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1988</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,10 +3875,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720504</v>
+        <v>720709</v>
       </c>
       <c r="R34" t="n">
-        <v>6626377</v>
+        <v>6626234</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3944,10 +3937,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128985852</v>
+        <v>128985868</v>
       </c>
       <c r="B35" t="n">
-        <v>92868</v>
+        <v>101325</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3955,37 +3948,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720548</v>
+        <v>720769</v>
       </c>
       <c r="R35" t="n">
-        <v>6626285</v>
+        <v>6626216</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4026,7 +4016,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4045,10 +4034,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128985889</v>
+        <v>128985907</v>
       </c>
       <c r="B36" t="n">
-        <v>92868</v>
+        <v>101325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4056,37 +4045,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720564</v>
+        <v>720516</v>
       </c>
       <c r="R36" t="n">
-        <v>6626459</v>
+        <v>6626359</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4127,7 +4113,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4146,51 +4131,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128985879</v>
+        <v>132011507</v>
       </c>
       <c r="B37" t="n">
-        <v>92868</v>
+        <v>91993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
+        <v>6332881</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720754</v>
+        <v>720505</v>
       </c>
       <c r="R37" t="n">
-        <v>6626384</v>
+        <v>6626362</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4214,12 +4191,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4228,51 +4205,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128985876</v>
+        <v>128985883</v>
       </c>
       <c r="B38" t="n">
-        <v>92505</v>
+        <v>89799</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>37</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4282,10 +4258,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720766</v>
+        <v>720621</v>
       </c>
       <c r="R38" t="n">
-        <v>6626378</v>
+        <v>6626429</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4318,6 +4294,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4344,32 +4325,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128985859</v>
+        <v>128985873</v>
       </c>
       <c r="B39" t="n">
-        <v>92505</v>
+        <v>87238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4379,10 +4360,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720718</v>
+        <v>720771</v>
       </c>
       <c r="R39" t="n">
-        <v>6626247</v>
+        <v>6626378</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4441,10 +4422,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128985906</v>
+        <v>128985882</v>
       </c>
       <c r="B40" t="n">
-        <v>92821</v>
+        <v>92292</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4452,34 +4433,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>150</v>
+        <v>1506</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720486</v>
+        <v>720643</v>
       </c>
       <c r="R40" t="n">
-        <v>6626330</v>
+        <v>6626413</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4514,6 +4498,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4522,6 +4511,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4538,48 +4547,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128985895</v>
+        <v>128985908</v>
       </c>
       <c r="B41" t="n">
-        <v>92868</v>
+        <v>87322</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720572</v>
+        <v>720504</v>
       </c>
       <c r="R41" t="n">
-        <v>6626395</v>
+        <v>6626377</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4620,7 +4626,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4639,10 +4644,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128985885</v>
+        <v>128985898</v>
       </c>
       <c r="B42" t="n">
-        <v>92868</v>
+        <v>91680</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4650,37 +4655,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720573</v>
+        <v>720530</v>
       </c>
       <c r="R42" t="n">
-        <v>6626380</v>
+        <v>6626369</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4721,7 +4723,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4740,48 +4741,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128985896</v>
+        <v>128985890</v>
       </c>
       <c r="B43" t="n">
-        <v>92868</v>
+        <v>87247</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720577</v>
+        <v>720530</v>
       </c>
       <c r="R43" t="n">
-        <v>6626370</v>
+        <v>6626415</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4822,7 +4820,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4841,38 +4838,35 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128985875</v>
+        <v>128985878</v>
       </c>
       <c r="B44" t="n">
-        <v>92868</v>
+        <v>93215</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
@@ -4882,7 +4876,7 @@
         <v>720769</v>
       </c>
       <c r="R44" t="n">
-        <v>6626395</v>
+        <v>6626378</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4923,7 +4917,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4942,32 +4935,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128985873</v>
+        <v>128985876</v>
       </c>
       <c r="B45" t="n">
-        <v>86897</v>
+        <v>92869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>445</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,7 +4970,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720771</v>
+        <v>720766</v>
       </c>
       <c r="R45" t="n">
         <v>6626378</v>
@@ -5039,48 +5032,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128985882</v>
+        <v>128985886</v>
       </c>
       <c r="B46" t="n">
-        <v>91932</v>
+        <v>92869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720643</v>
+        <v>720581</v>
       </c>
       <c r="R46" t="n">
-        <v>6626413</v>
+        <v>6626397</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5115,11 +5105,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5128,26 +5113,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5164,10 +5129,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128985902</v>
+        <v>128985900</v>
       </c>
       <c r="B47" t="n">
-        <v>92505</v>
+        <v>92869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5199,10 +5164,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720521</v>
+        <v>720544</v>
       </c>
       <c r="R47" t="n">
-        <v>6626387</v>
+        <v>6626397</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5261,10 +5226,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128985899</v>
+        <v>128985901</v>
       </c>
       <c r="B48" t="n">
-        <v>58584</v>
+        <v>92869</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,21 +5237,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208250</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5261,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720542</v>
+        <v>720521</v>
       </c>
       <c r="R48" t="n">
-        <v>6626391</v>
+        <v>6626398</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5358,10 +5323,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131431262</v>
+        <v>128985902</v>
       </c>
       <c r="B49" t="n">
-        <v>93134</v>
+        <v>92869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5369,37 +5334,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720598</v>
+        <v>720521</v>
       </c>
       <c r="R49" t="n">
-        <v>6626321</v>
+        <v>6626387</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5423,12 +5388,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5443,26 +5408,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karina Hälleberg</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Värdefull natur i Stockholms län</t>
-        </is>
-      </c>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131431264</v>
+        <v>128985875</v>
       </c>
       <c r="B50" t="n">
-        <v>57909</v>
+        <v>93233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5470,37 +5431,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720729</v>
+        <v>720769</v>
       </c>
       <c r="R50" t="n">
-        <v>6626290</v>
+        <v>6626395</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5524,12 +5488,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5538,25 +5502,1435 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Karina Hälleberg</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Värdefull natur i Stockholms län</t>
-        </is>
-      </c>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128985879</v>
+      </c>
+      <c r="B51" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>720754</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6626384</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128985885</v>
+      </c>
+      <c r="B52" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>720573</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6626380</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128985888</v>
+      </c>
+      <c r="B53" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>720578</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6626426</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128985889</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>720564</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6626459</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128985894</v>
+      </c>
+      <c r="B55" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>720563</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6626412</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128985895</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>720572</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6626395</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128985896</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>720577</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6626370</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128985891</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>720531</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6626414</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128985893</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>720574</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6626394</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128985899</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>720542</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6626391</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124665953</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bollen, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>720564</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6626375</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128985884</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>720568</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6626387</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>124664322</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Holmängsviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6626379</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128985887</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106230</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>720586</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6626407</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985883</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985851</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985853</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985903</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985873</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985860</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985866</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985882</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663540</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1869,6 +1929,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985849</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985908</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2063,6 +2133,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985898</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431263</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,6 +2341,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985890</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2358,6 +2443,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985867</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2455,6 +2545,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985857</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2556,6 +2651,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431262</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2653,6 +2753,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985904</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2750,6 +2855,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985878</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2847,6 +2957,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985850</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2944,6 +3059,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985856</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3041,6 +3161,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985859</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3138,6 +3263,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985876</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3235,6 +3365,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985886</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3332,6 +3467,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985900</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3429,6 +3569,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985901</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3526,6 +3671,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985902</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3623,6 +3773,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985862</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3724,6 +3879,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985839</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3825,6 +3985,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985846</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3926,6 +4091,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985847</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4027,6 +4197,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985852</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4128,6 +4303,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985854</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4229,6 +4409,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985861</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4330,6 +4515,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985863</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4431,6 +4621,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985865</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4532,6 +4727,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985875</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4633,6 +4833,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985879</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4734,6 +4939,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985885</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4835,6 +5045,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985888</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4936,6 +5151,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985889</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5037,6 +5257,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985894</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5138,6 +5363,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985895</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5239,6 +5469,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985896</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5340,6 +5575,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985897</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5441,6 +5681,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985905</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5542,6 +5787,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985912</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5657,6 +5907,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985891</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5759,6 +6014,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663137</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5860,6 +6120,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431264</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5957,6 +6222,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985893</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6054,6 +6324,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985899</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6160,6 +6435,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124665953</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6257,6 +6537,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985884</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6354,6 +6639,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663221</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6451,6 +6741,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664322</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6548,6 +6843,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985858</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6645,6 +6945,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985868</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6742,6 +7047,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985907</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6839,6 +7149,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985887</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6931,8 +7246,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93215</v>
+        <v>93365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21837-2025 artfynd.xlsx
+++ b/artfynd/A 21837-2025 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>128985878</v>
       </c>
       <c r="B22" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
